--- a/backend/data/songs-source-06-2026.xlsx
+++ b/backend/data/songs-source-06-2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josef.prochazka\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\josefprochazka\repos-ubuntu\songs-names-analyzer\backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63FCA501-5192-4EC3-A4E0-0E2DA35E5266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD74778-891C-46B3-9BCA-A04F0F29A00D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DATA" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="93">
   <si>
     <t>Ježíš Kristus, On je král</t>
   </si>
@@ -299,12 +299,6 @@
   </si>
   <si>
     <t>Velký ty</t>
-  </si>
-  <si>
-    <t>Ty jsi má skála</t>
-  </si>
-  <si>
-    <t>Před Božím trůnem</t>
   </si>
 </sst>
 </file>
@@ -587,9 +581,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F583"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1">
         <v>45186</v>
       </c>
@@ -597,7 +591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>45186</v>
       </c>
@@ -605,7 +599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>45186</v>
       </c>
@@ -613,7 +607,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>45186</v>
       </c>
@@ -621,7 +615,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>45186</v>
       </c>
@@ -629,7 +623,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>45193</v>
       </c>
@@ -637,7 +631,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>45193</v>
       </c>
@@ -645,7 +639,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>45193</v>
       </c>
@@ -653,7 +647,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>45193</v>
       </c>
@@ -665,7 +659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>45193</v>
       </c>
@@ -673,7 +667,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>45200</v>
       </c>
@@ -681,7 +675,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>45200</v>
       </c>
@@ -689,7 +683,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>45200</v>
       </c>
@@ -697,7 +691,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>45200</v>
       </c>
@@ -705,7 +699,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>45200</v>
       </c>
@@ -713,7 +707,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>45207</v>
       </c>
@@ -721,7 +715,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>45207</v>
       </c>
@@ -729,7 +723,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>45207</v>
       </c>
@@ -737,7 +731,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>45214</v>
       </c>
@@ -745,7 +739,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>45214</v>
       </c>
@@ -753,7 +747,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>45214</v>
       </c>
@@ -761,7 +755,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>45221</v>
       </c>
@@ -769,7 +763,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>45221</v>
       </c>
@@ -777,7 +771,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>45221</v>
       </c>
@@ -785,7 +779,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>45228</v>
       </c>
@@ -793,7 +787,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>45228</v>
       </c>
@@ -801,7 +795,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>45228</v>
       </c>
@@ -809,7 +803,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>45235</v>
       </c>
@@ -817,7 +811,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>45235</v>
       </c>
@@ -825,7 +819,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>45235</v>
       </c>
@@ -833,7 +827,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>45242</v>
       </c>
@@ -841,7 +835,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>45242</v>
       </c>
@@ -849,7 +843,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>45242</v>
       </c>
@@ -857,7 +851,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>45249</v>
       </c>
@@ -865,7 +859,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>45249</v>
       </c>
@@ -873,7 +867,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>45249</v>
       </c>
@@ -881,7 +875,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>45256</v>
       </c>
@@ -889,7 +883,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>45256</v>
       </c>
@@ -897,7 +891,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>45256</v>
       </c>
@@ -905,7 +899,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>45256</v>
       </c>
@@ -913,7 +907,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>45263</v>
       </c>
@@ -921,7 +915,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>45263</v>
       </c>
@@ -929,7 +923,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>45263</v>
       </c>
@@ -937,7 +931,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>45263</v>
       </c>
@@ -945,7 +939,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>45270</v>
       </c>
@@ -953,7 +947,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>45270</v>
       </c>
@@ -961,7 +955,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>45270</v>
       </c>
@@ -969,7 +963,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>45270</v>
       </c>
@@ -977,7 +971,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>45277</v>
       </c>
@@ -985,7 +979,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>45277</v>
       </c>
@@ -993,7 +987,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>45277</v>
       </c>
@@ -1001,7 +995,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>45277</v>
       </c>
@@ -1009,7 +1003,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>45284</v>
       </c>
@@ -1017,7 +1011,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>45284</v>
       </c>
@@ -1025,7 +1019,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>45284</v>
       </c>
@@ -1033,7 +1027,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
         <v>45284</v>
       </c>
@@ -1041,7 +1035,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <v>45291</v>
       </c>
@@ -1049,7 +1043,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
         <v>45291</v>
       </c>
@@ -1057,7 +1051,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
         <v>45291</v>
       </c>
@@ -1065,7 +1059,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
         <v>45291</v>
       </c>
@@ -1073,7 +1067,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>45298</v>
       </c>
@@ -1081,7 +1075,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>45298</v>
       </c>
@@ -1089,7 +1083,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>45298</v>
       </c>
@@ -1097,7 +1091,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>45298</v>
       </c>
@@ -1105,7 +1099,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>45305</v>
       </c>
@@ -1113,7 +1107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>45305</v>
       </c>
@@ -1121,7 +1115,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>45305</v>
       </c>
@@ -1129,7 +1123,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>45305</v>
       </c>
@@ -1137,7 +1131,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>45312</v>
       </c>
@@ -1145,7 +1139,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>45312</v>
       </c>
@@ -1153,7 +1147,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>45312</v>
       </c>
@@ -1161,7 +1155,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>45312</v>
       </c>
@@ -1169,7 +1163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>45319</v>
       </c>
@@ -1177,7 +1171,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>45319</v>
       </c>
@@ -1185,7 +1179,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>45319</v>
       </c>
@@ -1193,7 +1187,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>45319</v>
       </c>
@@ -1201,7 +1195,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>45326</v>
       </c>
@@ -1209,7 +1203,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>45326</v>
       </c>
@@ -1217,7 +1211,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>45326</v>
       </c>
@@ -1225,7 +1219,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>45326</v>
       </c>
@@ -1233,7 +1227,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>45333</v>
       </c>
@@ -1241,7 +1235,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>45333</v>
       </c>
@@ -1249,7 +1243,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>45333</v>
       </c>
@@ -1257,7 +1251,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>45333</v>
       </c>
@@ -1265,7 +1259,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>45340</v>
       </c>
@@ -1273,7 +1267,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>45340</v>
       </c>
@@ -1281,7 +1275,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>45340</v>
       </c>
@@ -1289,7 +1283,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>45340</v>
       </c>
@@ -1297,7 +1291,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>45347</v>
       </c>
@@ -1305,7 +1299,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>45347</v>
       </c>
@@ -1313,7 +1307,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>45347</v>
       </c>
@@ -1321,7 +1315,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>45347</v>
       </c>
@@ -1329,7 +1323,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>45354</v>
       </c>
@@ -1337,7 +1331,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>45354</v>
       </c>
@@ -1345,7 +1339,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>45354</v>
       </c>
@@ -1353,7 +1347,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>45354</v>
       </c>
@@ -1361,7 +1355,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>45361</v>
       </c>
@@ -1369,7 +1363,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>45361</v>
       </c>
@@ -1377,7 +1371,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>45361</v>
       </c>
@@ -1385,7 +1379,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>45361</v>
       </c>
@@ -1393,7 +1387,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>45368</v>
       </c>
@@ -1401,7 +1395,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>45368</v>
       </c>
@@ -1409,7 +1403,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>45368</v>
       </c>
@@ -1417,7 +1411,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>45368</v>
       </c>
@@ -1425,7 +1419,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>45375</v>
       </c>
@@ -1433,7 +1427,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>45375</v>
       </c>
@@ -1441,7 +1435,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>45375</v>
       </c>
@@ -1449,7 +1443,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>45375</v>
       </c>
@@ -1457,7 +1451,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>45382</v>
       </c>
@@ -1465,7 +1459,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>45382</v>
       </c>
@@ -1473,7 +1467,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>45382</v>
       </c>
@@ -1481,7 +1475,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>45382</v>
       </c>
@@ -1489,7 +1483,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>45389</v>
       </c>
@@ -1497,7 +1491,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>45389</v>
       </c>
@@ -1505,7 +1499,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>45389</v>
       </c>
@@ -1513,7 +1507,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>45389</v>
       </c>
@@ -1521,7 +1515,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>45396</v>
       </c>
@@ -1529,7 +1523,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>45396</v>
       </c>
@@ -1537,7 +1531,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>45396</v>
       </c>
@@ -1545,7 +1539,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>45396</v>
       </c>
@@ -1553,7 +1547,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>45403</v>
       </c>
@@ -1561,7 +1555,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>45403</v>
       </c>
@@ -1569,7 +1563,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>45403</v>
       </c>
@@ -1577,7 +1571,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>45403</v>
       </c>
@@ -1585,7 +1579,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>45410</v>
       </c>
@@ -1593,7 +1587,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>45410</v>
       </c>
@@ -1601,7 +1595,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>45410</v>
       </c>
@@ -1609,7 +1603,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>45410</v>
       </c>
@@ -1617,7 +1611,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>45417</v>
       </c>
@@ -1625,7 +1619,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>45417</v>
       </c>
@@ -1633,7 +1627,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>45417</v>
       </c>
@@ -1641,7 +1635,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>45417</v>
       </c>
@@ -1649,7 +1643,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>45424</v>
       </c>
@@ -1657,7 +1651,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>45424</v>
       </c>
@@ -1665,7 +1659,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>45424</v>
       </c>
@@ -1673,7 +1667,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>45424</v>
       </c>
@@ -1681,7 +1675,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>45431</v>
       </c>
@@ -1689,7 +1683,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>45431</v>
       </c>
@@ -1697,7 +1691,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>45431</v>
       </c>
@@ -1705,7 +1699,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>45431</v>
       </c>
@@ -1713,7 +1707,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>45438</v>
       </c>
@@ -1721,7 +1715,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>45438</v>
       </c>
@@ -1729,7 +1723,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>45438</v>
       </c>
@@ -1737,7 +1731,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>45438</v>
       </c>
@@ -1745,7 +1739,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>45445</v>
       </c>
@@ -1753,7 +1747,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>45445</v>
       </c>
@@ -1761,7 +1755,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>45445</v>
       </c>
@@ -1769,7 +1763,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>45445</v>
       </c>
@@ -1777,7 +1771,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>45452</v>
       </c>
@@ -1785,7 +1779,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>45452</v>
       </c>
@@ -1793,7 +1787,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>45452</v>
       </c>
@@ -1801,7 +1795,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>45452</v>
       </c>
@@ -1809,7 +1803,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>45459</v>
       </c>
@@ -1817,7 +1811,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>45459</v>
       </c>
@@ -1825,7 +1819,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>45459</v>
       </c>
@@ -1833,7 +1827,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>45459</v>
       </c>
@@ -1841,7 +1835,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>45466</v>
       </c>
@@ -1849,7 +1843,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>45466</v>
       </c>
@@ -1857,7 +1851,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>45466</v>
       </c>
@@ -1865,7 +1859,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>45466</v>
       </c>
@@ -1873,7 +1867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>45473</v>
       </c>
@@ -1881,7 +1875,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>45473</v>
       </c>
@@ -1889,7 +1883,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>45473</v>
       </c>
@@ -1897,7 +1891,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>45473</v>
       </c>
@@ -1905,7 +1899,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>45480</v>
       </c>
@@ -1913,7 +1907,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>45480</v>
       </c>
@@ -1921,7 +1915,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>45480</v>
       </c>
@@ -1929,7 +1923,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>45480</v>
       </c>
@@ -1937,7 +1931,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>45487</v>
       </c>
@@ -1945,7 +1939,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>45487</v>
       </c>
@@ -1953,7 +1947,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>45487</v>
       </c>
@@ -1961,7 +1955,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>45487</v>
       </c>
@@ -1969,7 +1963,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>45494</v>
       </c>
@@ -1977,7 +1971,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>45494</v>
       </c>
@@ -1985,7 +1979,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>45494</v>
       </c>
@@ -1993,7 +1987,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>45494</v>
       </c>
@@ -2001,7 +1995,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>45494</v>
       </c>
@@ -2009,7 +2003,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>45501</v>
       </c>
@@ -2017,7 +2011,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>45501</v>
       </c>
@@ -2025,7 +2019,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>45501</v>
       </c>
@@ -2033,7 +2027,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>45501</v>
       </c>
@@ -2041,7 +2035,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>45508</v>
       </c>
@@ -2049,7 +2043,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>45508</v>
       </c>
@@ -2057,7 +2051,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>45508</v>
       </c>
@@ -2065,7 +2059,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>45508</v>
       </c>
@@ -2073,7 +2067,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>45515</v>
       </c>
@@ -2081,7 +2075,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>45515</v>
       </c>
@@ -2089,7 +2083,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>45515</v>
       </c>
@@ -2097,7 +2091,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>45515</v>
       </c>
@@ -2105,7 +2099,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>45522</v>
       </c>
@@ -2113,7 +2107,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>45522</v>
       </c>
@@ -2121,7 +2115,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>45522</v>
       </c>
@@ -2129,7 +2123,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>45522</v>
       </c>
@@ -2137,7 +2131,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>45529</v>
       </c>
@@ -2145,7 +2139,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>45529</v>
       </c>
@@ -2153,7 +2147,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>45529</v>
       </c>
@@ -2161,7 +2155,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <v>45529</v>
       </c>
@@ -2169,7 +2163,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>45543</v>
       </c>
@@ -2177,7 +2171,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>45543</v>
       </c>
@@ -2185,7 +2179,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>45543</v>
       </c>
@@ -2193,7 +2187,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <v>45543</v>
       </c>
@@ -2201,7 +2195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
         <v>45550</v>
       </c>
@@ -2209,7 +2203,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <v>45550</v>
       </c>
@@ -2217,7 +2211,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <v>45550</v>
       </c>
@@ -2225,7 +2219,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>45550</v>
       </c>
@@ -2233,7 +2227,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <v>45557</v>
       </c>
@@ -2241,7 +2235,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <v>45557</v>
       </c>
@@ -2249,7 +2243,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <v>45557</v>
       </c>
@@ -2257,7 +2251,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <v>45557</v>
       </c>
@@ -2265,7 +2259,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <v>45564</v>
       </c>
@@ -2273,7 +2267,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
         <v>45564</v>
       </c>
@@ -2281,7 +2275,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
         <v>45564</v>
       </c>
@@ -2289,7 +2283,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
         <v>45564</v>
       </c>
@@ -2297,7 +2291,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
         <v>45571</v>
       </c>
@@ -2305,7 +2299,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
         <v>45571</v>
       </c>
@@ -2313,7 +2307,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
         <v>45571</v>
       </c>
@@ -2321,7 +2315,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
         <v>45571</v>
       </c>
@@ -2329,7 +2323,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A218" s="4">
         <v>45578</v>
       </c>
@@ -2337,7 +2331,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A219" s="4">
         <v>45578</v>
       </c>
@@ -2345,7 +2339,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A220" s="4">
         <v>45578</v>
       </c>
@@ -2353,7 +2347,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A221" s="4">
         <v>45578</v>
       </c>
@@ -2361,7 +2355,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A222" s="4">
         <v>45585</v>
       </c>
@@ -2369,7 +2363,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A223" s="4">
         <v>45585</v>
       </c>
@@ -2377,7 +2371,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A224" s="4">
         <v>45585</v>
       </c>
@@ -2385,7 +2379,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A225" s="4">
         <v>45585</v>
       </c>
@@ -2393,7 +2387,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A226" s="4">
         <v>45592</v>
       </c>
@@ -2401,7 +2395,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A227" s="4">
         <v>45592</v>
       </c>
@@ -2409,7 +2403,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A228" s="4">
         <v>45592</v>
       </c>
@@ -2417,7 +2411,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A229" s="4">
         <v>45592</v>
       </c>
@@ -2425,7 +2419,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
         <v>45599</v>
       </c>
@@ -2433,7 +2427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
         <v>45599</v>
       </c>
@@ -2441,7 +2435,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
         <v>45599</v>
       </c>
@@ -2449,7 +2443,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
         <v>45599</v>
       </c>
@@ -2457,7 +2451,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A234" s="4">
         <v>45606</v>
       </c>
@@ -2465,7 +2459,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A235" s="4">
         <v>45606</v>
       </c>
@@ -2473,7 +2467,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A236" s="4">
         <v>45606</v>
       </c>
@@ -2481,7 +2475,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A237" s="4">
         <v>45606</v>
       </c>
@@ -2489,7 +2483,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A238" s="4">
         <v>45606</v>
       </c>
@@ -2497,7 +2491,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A239" s="4">
         <v>45613</v>
       </c>
@@ -2505,7 +2499,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A240" s="4">
         <v>45613</v>
       </c>
@@ -2513,7 +2507,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A241" s="4">
         <v>45613</v>
       </c>
@@ -2521,7 +2515,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A242" s="4">
         <v>45613</v>
       </c>
@@ -2529,7 +2523,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A243" s="4">
         <v>45620</v>
       </c>
@@ -2537,7 +2531,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A244" s="4">
         <v>45620</v>
       </c>
@@ -2545,7 +2539,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A245" s="4">
         <v>45620</v>
       </c>
@@ -2553,7 +2547,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A246" s="4">
         <v>45620</v>
       </c>
@@ -2561,7 +2555,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A247" s="4">
         <v>45620</v>
       </c>
@@ -2569,7 +2563,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
         <v>45627</v>
       </c>
@@ -2577,7 +2571,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
         <v>45627</v>
       </c>
@@ -2585,7 +2579,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
         <v>45627</v>
       </c>
@@ -2593,7 +2587,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
         <v>45627</v>
       </c>
@@ -2601,7 +2595,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
         <v>45634</v>
       </c>
@@ -2609,7 +2603,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
         <v>45634</v>
       </c>
@@ -2617,7 +2611,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
         <v>45634</v>
       </c>
@@ -2625,7 +2619,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
         <v>45634</v>
       </c>
@@ -2633,7 +2627,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A256" s="4">
         <v>45641</v>
       </c>
@@ -2641,7 +2635,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A257" s="4">
         <v>45641</v>
       </c>
@@ -2649,7 +2643,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A258" s="4">
         <v>45641</v>
       </c>
@@ -2657,7 +2651,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A259" s="4">
         <v>45641</v>
       </c>
@@ -2665,7 +2659,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A260" s="4">
         <v>45648</v>
       </c>
@@ -2673,7 +2667,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A261" s="4">
         <v>45648</v>
       </c>
@@ -2681,7 +2675,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A262" s="4">
         <v>45648</v>
       </c>
@@ -2689,7 +2683,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A263" s="4">
         <v>45648</v>
       </c>
@@ -2697,7 +2691,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A264" s="4">
         <v>45648</v>
       </c>
@@ -2705,7 +2699,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A265" s="4">
         <v>45655</v>
       </c>
@@ -2713,7 +2707,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A266" s="4">
         <v>45655</v>
       </c>
@@ -2721,7 +2715,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A267" s="4">
         <v>45655</v>
       </c>
@@ -2729,7 +2723,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A268" s="4">
         <v>45655</v>
       </c>
@@ -2737,7 +2731,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
         <v>45662</v>
       </c>
@@ -2745,7 +2739,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
         <v>45662</v>
       </c>
@@ -2753,7 +2747,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
         <v>45662</v>
       </c>
@@ -2761,7 +2755,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
         <v>45662</v>
       </c>
@@ -2769,7 +2763,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
         <v>45669</v>
       </c>
@@ -2777,7 +2771,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
         <v>45669</v>
       </c>
@@ -2785,7 +2779,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A275" s="1">
         <v>45669</v>
       </c>
@@ -2793,7 +2787,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
         <v>45669</v>
       </c>
@@ -2801,7 +2795,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
         <v>45676</v>
       </c>
@@ -2809,7 +2803,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
         <v>45676</v>
       </c>
@@ -2817,7 +2811,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
         <v>45676</v>
       </c>
@@ -2825,7 +2819,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
         <v>45676</v>
       </c>
@@ -2833,7 +2827,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
         <v>45683</v>
       </c>
@@ -2841,7 +2835,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
         <v>45683</v>
       </c>
@@ -2849,7 +2843,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
         <v>45683</v>
       </c>
@@ -2857,7 +2851,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A284" s="1">
         <v>45683</v>
       </c>
@@ -2865,7 +2859,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A285" s="1">
         <v>45690</v>
       </c>
@@ -2873,7 +2867,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A286" s="1">
         <v>45690</v>
       </c>
@@ -2881,7 +2875,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A287" s="1">
         <v>45690</v>
       </c>
@@ -2889,7 +2883,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A288" s="1">
         <v>45690</v>
       </c>
@@ -2897,7 +2891,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A289" s="1">
         <v>45697</v>
       </c>
@@ -2905,7 +2899,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
         <v>45697</v>
       </c>
@@ -2913,7 +2907,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A291" s="1">
         <v>45697</v>
       </c>
@@ -2921,7 +2915,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
         <v>45697</v>
       </c>
@@ -2929,7 +2923,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A293" s="1">
         <v>45704</v>
       </c>
@@ -2937,7 +2931,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A294" s="1">
         <v>45704</v>
       </c>
@@ -2945,7 +2939,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A295" s="1">
         <v>45704</v>
       </c>
@@ -2953,7 +2947,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A296" s="1">
         <v>45704</v>
       </c>
@@ -2961,7 +2955,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
         <v>45711</v>
       </c>
@@ -2969,7 +2963,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
         <v>45711</v>
       </c>
@@ -2977,7 +2971,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A299" s="1">
         <v>45711</v>
       </c>
@@ -2985,7 +2979,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A300" s="1">
         <v>45711</v>
       </c>
@@ -2993,7 +2987,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A301" s="1">
         <v>45718</v>
       </c>
@@ -3001,7 +2995,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A302" s="1">
         <v>45718</v>
       </c>
@@ -3009,7 +3003,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A303" s="1">
         <v>45718</v>
       </c>
@@ -3017,7 +3011,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
         <v>45718</v>
       </c>
@@ -3025,7 +3019,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
         <v>45725</v>
       </c>
@@ -3033,7 +3027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
         <v>45725</v>
       </c>
@@ -3041,7 +3035,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
         <v>45725</v>
       </c>
@@ -3049,7 +3043,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
         <v>45725</v>
       </c>
@@ -3057,7 +3051,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A309" s="1">
         <v>45732</v>
       </c>
@@ -3065,7 +3059,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A310" s="1">
         <v>45732</v>
       </c>
@@ -3073,7 +3067,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A311" s="1">
         <v>45732</v>
       </c>
@@ -3081,7 +3075,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A312" s="1">
         <v>45732</v>
       </c>
@@ -3089,7 +3083,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A313" s="1">
         <v>45739</v>
       </c>
@@ -3097,7 +3091,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A314" s="1">
         <v>45739</v>
       </c>
@@ -3105,7 +3099,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="315" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A315" s="1">
         <v>45739</v>
       </c>
@@ -3113,7 +3107,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="316" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A316" s="1">
         <v>45739</v>
       </c>
@@ -3121,7 +3115,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="317" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A317" s="1">
         <v>45746</v>
       </c>
@@ -3129,7 +3123,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="318" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A318" s="1">
         <v>45746</v>
       </c>
@@ -3137,7 +3131,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="319" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A319" s="1">
         <v>45746</v>
       </c>
@@ -3145,7 +3139,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="320" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A320" s="1">
         <v>45746</v>
       </c>
@@ -3153,7 +3147,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="321" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A321" s="1">
         <v>45753</v>
       </c>
@@ -3161,7 +3155,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A322" s="1">
         <v>45753</v>
       </c>
@@ -3169,7 +3163,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="323" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A323" s="1">
         <v>45753</v>
       </c>
@@ -3177,7 +3171,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A324" s="1">
         <v>45753</v>
       </c>
@@ -3185,7 +3179,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A325" s="1">
         <v>45760</v>
       </c>
@@ -3193,7 +3187,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A326" s="1">
         <v>45760</v>
       </c>
@@ -3201,7 +3195,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A327" s="1">
         <v>45760</v>
       </c>
@@ -3209,7 +3203,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="328" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A328" s="1">
         <v>45760</v>
       </c>
@@ -3217,7 +3211,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A329" s="1">
         <v>45767</v>
       </c>
@@ -3225,7 +3219,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A330" s="1">
         <v>45767</v>
       </c>
@@ -3233,7 +3227,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A331" s="1">
         <v>45767</v>
       </c>
@@ -3241,7 +3235,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A332" s="1">
         <v>45767</v>
       </c>
@@ -3249,7 +3243,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A333" s="1">
         <v>45767</v>
       </c>
@@ -3257,7 +3251,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A334" s="1">
         <v>45774</v>
       </c>
@@ -3265,7 +3259,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A335" s="1">
         <v>45774</v>
       </c>
@@ -3273,7 +3267,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A336" s="1">
         <v>45774</v>
       </c>
@@ -3281,7 +3275,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A337" s="1">
         <v>45774</v>
       </c>
@@ -3289,7 +3283,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A338" s="1">
         <v>45781</v>
       </c>
@@ -3297,7 +3291,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A339" s="1">
         <v>45781</v>
       </c>
@@ -3305,7 +3299,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A340" s="1">
         <v>45781</v>
       </c>
@@ -3313,7 +3307,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A341" s="1">
         <v>45781</v>
       </c>
@@ -3321,7 +3315,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A342" s="1">
         <v>45788</v>
       </c>
@@ -3329,7 +3323,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A343" s="1">
         <v>45788</v>
       </c>
@@ -3337,7 +3331,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A344" s="1">
         <v>45788</v>
       </c>
@@ -3345,7 +3339,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A345" s="1">
         <v>45788</v>
       </c>
@@ -3353,7 +3347,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A346" s="1">
         <v>45795</v>
       </c>
@@ -3361,7 +3355,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A347" s="1">
         <v>45795</v>
       </c>
@@ -3369,7 +3363,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A348" s="1">
         <v>45795</v>
       </c>
@@ -3377,7 +3371,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="349" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A349" s="1">
         <v>45795</v>
       </c>
@@ -3385,7 +3379,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A350" s="1">
         <v>45802</v>
       </c>
@@ -3393,7 +3387,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="351" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A351" s="1">
         <v>45802</v>
       </c>
@@ -3401,7 +3395,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="352" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A352" s="1">
         <v>45802</v>
       </c>
@@ -3409,7 +3403,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="353" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A353" s="1">
         <v>45802</v>
       </c>
@@ -3417,7 +3411,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="354" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A354" s="1">
         <v>45809</v>
       </c>
@@ -3425,7 +3419,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="355" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A355" s="1">
         <v>45809</v>
       </c>
@@ -3433,7 +3427,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="356" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A356" s="1">
         <v>45809</v>
       </c>
@@ -3441,7 +3435,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="357" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A357" s="1">
         <v>45809</v>
       </c>
@@ -3449,7 +3443,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="358" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A358" s="1">
         <v>45816</v>
       </c>
@@ -3457,7 +3451,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="359" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A359" s="1">
         <v>45816</v>
       </c>
@@ -3465,7 +3459,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="360" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A360" s="1">
         <v>45816</v>
       </c>
@@ -3473,7 +3467,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="361" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A361" s="1">
         <v>45816</v>
       </c>
@@ -3481,7 +3475,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="362" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A362" s="1">
         <v>45823</v>
       </c>
@@ -3489,7 +3483,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="363" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A363" s="1">
         <v>45823</v>
       </c>
@@ -3497,7 +3491,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="364" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A364" s="1">
         <v>45823</v>
       </c>
@@ -3505,7 +3499,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="365" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A365" s="1">
         <v>45823</v>
       </c>
@@ -3513,7 +3507,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="366" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A366" s="1">
         <v>45830</v>
       </c>
@@ -3521,7 +3515,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="367" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A367" s="1">
         <v>45830</v>
       </c>
@@ -3529,7 +3523,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="368" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A368" s="1">
         <v>45830</v>
       </c>
@@ -3537,7 +3531,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="369" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A369" s="1">
         <v>45830</v>
       </c>
@@ -3545,7 +3539,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="370" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A370" s="1">
         <v>45837</v>
       </c>
@@ -3553,7 +3547,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="371" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A371" s="1">
         <v>45837</v>
       </c>
@@ -3561,7 +3555,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="372" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A372" s="1">
         <v>45837</v>
       </c>
@@ -3569,7 +3563,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="373" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A373" s="1">
         <v>45837</v>
       </c>
@@ -3577,7 +3571,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="374" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A374" s="1">
         <v>45844</v>
       </c>
@@ -3585,7 +3579,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="375" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A375" s="1">
         <v>45844</v>
       </c>
@@ -3593,7 +3587,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="376" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A376" s="1">
         <v>45844</v>
       </c>
@@ -3601,7 +3595,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="377" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A377" s="1">
         <v>45844</v>
       </c>
@@ -3609,7 +3603,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="378" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A378" s="1">
         <v>45851</v>
       </c>
@@ -3617,7 +3611,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="379" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A379" s="1">
         <v>45851</v>
       </c>
@@ -3625,7 +3619,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="380" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A380" s="1">
         <v>45851</v>
       </c>
@@ -3633,7 +3627,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="381" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A381" s="1">
         <v>45851</v>
       </c>
@@ -3641,7 +3635,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="382" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A382" s="1">
         <v>45851</v>
       </c>
@@ -3649,7 +3643,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="383" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A383" s="1">
         <v>45858</v>
       </c>
@@ -3657,7 +3651,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="384" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A384" s="1">
         <v>45858</v>
       </c>
@@ -3665,7 +3659,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="385" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A385" s="1">
         <v>45858</v>
       </c>
@@ -3673,7 +3667,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="386" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A386" s="1">
         <v>45858</v>
       </c>
@@ -3681,7 +3675,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="387" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A387" s="1">
         <v>45865</v>
       </c>
@@ -3689,7 +3683,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="388" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A388" s="1">
         <v>45865</v>
       </c>
@@ -3697,7 +3691,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="389" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A389" s="1">
         <v>45865</v>
       </c>
@@ -3705,7 +3699,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="390" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A390" s="1">
         <v>45865</v>
       </c>
@@ -3713,7 +3707,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="391" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A391" s="1">
         <v>45872</v>
       </c>
@@ -3721,7 +3715,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="392" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A392" s="1">
         <v>45872</v>
       </c>
@@ -3729,7 +3723,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="393" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A393" s="1">
         <v>45872</v>
       </c>
@@ -3737,7 +3731,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="394" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A394" s="1">
         <v>45872</v>
       </c>
@@ -3745,7 +3739,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="395" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A395" s="1">
         <v>45879</v>
       </c>
@@ -3753,7 +3747,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="396" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A396" s="1">
         <v>45879</v>
       </c>
@@ -3761,7 +3755,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="397" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A397" s="1">
         <v>45879</v>
       </c>
@@ -3769,7 +3763,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="398" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A398" s="1">
         <v>45879</v>
       </c>
@@ -3777,7 +3771,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="399" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A399" s="1">
         <v>45886</v>
       </c>
@@ -3785,7 +3779,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="400" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A400" s="1">
         <v>45886</v>
       </c>
@@ -3793,7 +3787,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="401" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A401" s="1">
         <v>45886</v>
       </c>
@@ -3801,7 +3795,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="402" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A402" s="1">
         <v>45886</v>
       </c>
@@ -3809,7 +3803,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="403" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A403" s="1">
         <v>45893</v>
       </c>
@@ -3817,7 +3811,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="404" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A404" s="1">
         <v>45893</v>
       </c>
@@ -3825,7 +3819,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="405" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A405" s="1">
         <v>45893</v>
       </c>
@@ -3833,7 +3827,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="406" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A406" s="1">
         <v>45893</v>
       </c>
@@ -3841,7 +3835,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="407" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A407" s="1">
         <v>45907</v>
       </c>
@@ -3849,7 +3843,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="408" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A408" s="1">
         <v>45907</v>
       </c>
@@ -3857,7 +3851,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="409" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A409" s="1">
         <v>45907</v>
       </c>
@@ -3865,7 +3859,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="410" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A410" s="1">
         <v>45907</v>
       </c>
@@ -3873,7 +3867,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="411" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A411" s="1">
         <v>45907</v>
       </c>
@@ -3881,7 +3875,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="412" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A412" s="1">
         <v>45914</v>
       </c>
@@ -3889,7 +3883,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="413" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A413" s="1">
         <v>45914</v>
       </c>
@@ -3897,7 +3891,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="414" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A414" s="1">
         <v>45914</v>
       </c>
@@ -3905,7 +3899,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="415" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A415" s="1">
         <v>45914</v>
       </c>
@@ -3913,7 +3907,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="416" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A416" s="1">
         <v>45921</v>
       </c>
@@ -3921,7 +3915,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="417" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A417" s="1">
         <v>45921</v>
       </c>
@@ -3929,7 +3923,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="418" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A418" s="1">
         <v>45921</v>
       </c>
@@ -3937,7 +3931,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="419" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A419" s="1">
         <v>45921</v>
       </c>
@@ -3945,7 +3939,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="420" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A420" s="1">
         <v>45928</v>
       </c>
@@ -3953,7 +3947,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="421" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A421" s="1">
         <v>45928</v>
       </c>
@@ -3961,7 +3955,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="422" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A422" s="1">
         <v>45928</v>
       </c>
@@ -3969,7 +3963,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="423" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A423" s="1">
         <v>45928</v>
       </c>
@@ -3977,7 +3971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A424" s="1">
         <v>45935</v>
       </c>
@@ -3985,7 +3979,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="425" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A425" s="1">
         <v>45935</v>
       </c>
@@ -3993,7 +3987,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="426" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A426" s="1">
         <v>45935</v>
       </c>
@@ -4001,7 +3995,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="427" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A427" s="1">
         <v>45935</v>
       </c>
@@ -4009,7 +4003,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="428" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A428" s="4">
         <v>45942</v>
       </c>
@@ -4017,7 +4011,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="429" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A429" s="4">
         <v>45942</v>
       </c>
@@ -4025,7 +4019,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="430" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A430" s="4">
         <v>45942</v>
       </c>
@@ -4033,7 +4027,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="431" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A431" s="4">
         <v>45942</v>
       </c>
@@ -4041,7 +4035,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="432" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A432" s="4">
         <v>45949</v>
       </c>
@@ -4049,7 +4043,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="433" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A433" s="4">
         <v>45949</v>
       </c>
@@ -4057,7 +4051,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="434" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A434" s="4">
         <v>45949</v>
       </c>
@@ -4065,7 +4059,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="435" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A435" s="4">
         <v>45949</v>
       </c>
@@ -4073,7 +4067,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="436" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A436" s="4">
         <v>45956</v>
       </c>
@@ -4081,7 +4075,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="437" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A437" s="4">
         <v>45956</v>
       </c>
@@ -4089,7 +4083,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="438" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A438" s="4">
         <v>45956</v>
       </c>
@@ -4097,7 +4091,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="439" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A439" s="4">
         <v>45956</v>
       </c>
@@ -4105,7 +4099,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="440" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A440" s="1">
         <v>45963</v>
       </c>
@@ -4113,7 +4107,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="441" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A441" s="1">
         <v>45963</v>
       </c>
@@ -4121,7 +4115,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="442" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A442" s="1">
         <v>45963</v>
       </c>
@@ -4129,7 +4123,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="443" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A443" s="1">
         <v>45963</v>
       </c>
@@ -4137,7 +4131,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="444" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A444" s="1">
         <v>45970</v>
       </c>
@@ -4145,7 +4139,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="445" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A445" s="1">
         <v>45970</v>
       </c>
@@ -4153,7 +4147,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="446" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A446" s="1">
         <v>45970</v>
       </c>
@@ -4161,7 +4155,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="447" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A447" s="1">
         <v>45970</v>
       </c>
@@ -4169,7 +4163,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="448" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A448" s="4">
         <v>45977</v>
       </c>
@@ -4177,7 +4171,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="449" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A449" s="4">
         <v>45977</v>
       </c>
@@ -4185,7 +4179,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="450" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A450" s="4">
         <v>45977</v>
       </c>
@@ -4193,7 +4187,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="451" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A451" s="4">
         <v>45977</v>
       </c>
@@ -4201,7 +4195,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="452" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A452" s="4">
         <v>45984</v>
       </c>
@@ -4209,7 +4203,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="453" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A453" s="4">
         <v>45984</v>
       </c>
@@ -4217,7 +4211,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="454" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A454" s="4">
         <v>45984</v>
       </c>
@@ -4225,7 +4219,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="455" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A455" s="4">
         <v>45984</v>
       </c>
@@ -4233,7 +4227,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="456" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A456" s="4">
         <v>45991</v>
       </c>
@@ -4241,7 +4235,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="457" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A457" s="4">
         <v>45991</v>
       </c>
@@ -4249,7 +4243,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="458" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A458" s="4">
         <v>45991</v>
       </c>
@@ -4257,7 +4251,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="459" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A459" s="4">
         <v>45991</v>
       </c>
@@ -4265,7 +4259,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="460" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A460" s="1">
         <v>45998</v>
       </c>
@@ -4273,7 +4267,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="461" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A461" s="1">
         <v>45998</v>
       </c>
@@ -4281,7 +4275,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="462" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A462" s="1">
         <v>45998</v>
       </c>
@@ -4289,7 +4283,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="463" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A463" s="1">
         <v>45998</v>
       </c>
@@ -4297,7 +4291,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="464" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A464" s="4">
         <v>46005</v>
       </c>
@@ -4305,7 +4299,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="465" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A465" s="4">
         <v>46005</v>
       </c>
@@ -4313,7 +4307,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="466" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A466" s="4">
         <v>46005</v>
       </c>
@@ -4321,7 +4315,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="467" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A467" s="4">
         <v>46005</v>
       </c>
@@ -4329,7 +4323,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="468" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A468" s="4">
         <v>46012</v>
       </c>
@@ -4337,7 +4331,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="469" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A469" s="4">
         <v>46012</v>
       </c>
@@ -4345,7 +4339,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="470" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A470" s="4">
         <v>46012</v>
       </c>
@@ -4353,7 +4347,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="471" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A471" s="4">
         <v>46012</v>
       </c>
@@ -4361,7 +4355,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="472" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A472" s="4">
         <v>46012</v>
       </c>
@@ -4369,7 +4363,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="473" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A473" s="4">
         <v>46012</v>
       </c>
@@ -4377,7 +4371,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="474" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A474" s="4">
         <v>46012</v>
       </c>
@@ -4385,7 +4379,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="475" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A475" s="4">
         <v>46019</v>
       </c>
@@ -4393,7 +4387,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="476" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A476" s="4">
         <v>46019</v>
       </c>
@@ -4401,7 +4395,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="477" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A477" s="4">
         <v>46019</v>
       </c>
@@ -4409,7 +4403,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="478" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A478" s="4">
         <v>46019</v>
       </c>
@@ -4417,7 +4411,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="479" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A479" s="1">
         <v>46026</v>
       </c>
@@ -4425,7 +4419,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="480" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A480" s="1">
         <v>46026</v>
       </c>
@@ -4433,7 +4427,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="481" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A481" s="1">
         <v>46026</v>
       </c>
@@ -4441,7 +4435,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="482" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A482" s="1">
         <v>46026</v>
       </c>
@@ -4449,7 +4443,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="483" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A483" s="1">
         <v>46033</v>
       </c>
@@ -4457,7 +4451,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="484" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A484" s="1">
         <v>46033</v>
       </c>
@@ -4465,7 +4459,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="485" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A485" s="1">
         <v>46033</v>
       </c>
@@ -4473,7 +4467,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="486" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A486" s="1">
         <v>46033</v>
       </c>
@@ -4481,7 +4475,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="487" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A487" s="1">
         <v>46040</v>
       </c>
@@ -4489,7 +4483,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="488" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A488" s="1">
         <v>46040</v>
       </c>
@@ -4497,7 +4491,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="489" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A489" s="1">
         <v>46040</v>
       </c>
@@ -4505,7 +4499,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="490" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A490" s="1">
         <v>46040</v>
       </c>
@@ -4513,7 +4507,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="491" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A491" s="1">
         <v>46047</v>
       </c>
@@ -4521,7 +4515,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="492" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A492" s="1">
         <v>46047</v>
       </c>
@@ -4529,7 +4523,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="493" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A493" s="1">
         <v>46047</v>
       </c>
@@ -4537,7 +4531,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="494" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A494" s="1">
         <v>46047</v>
       </c>
@@ -4545,7 +4539,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="495" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A495" s="1">
         <v>46054</v>
       </c>
@@ -4553,7 +4547,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="496" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A496" s="1">
         <v>46054</v>
       </c>
@@ -4561,7 +4555,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="497" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A497" s="1">
         <v>46054</v>
       </c>
@@ -4569,7 +4563,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="498" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A498" s="1">
         <v>46054</v>
       </c>
@@ -4577,7 +4571,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="499" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A499" s="1">
         <v>46061</v>
       </c>
@@ -4585,7 +4579,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="500" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A500" s="1">
         <v>46061</v>
       </c>
@@ -4593,7 +4587,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="501" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A501" s="1">
         <v>46061</v>
       </c>
@@ -4601,7 +4595,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="502" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A502" s="1">
         <v>46061</v>
       </c>
@@ -4609,7 +4603,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="503" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A503" s="1">
         <v>46068</v>
       </c>
@@ -4617,7 +4611,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="504" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A504" s="1">
         <v>46068</v>
       </c>
@@ -4625,7 +4619,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="505" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A505" s="1">
         <v>46068</v>
       </c>
@@ -4633,7 +4627,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="506" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A506" s="1">
         <v>46068</v>
       </c>
@@ -4641,7 +4635,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="507" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A507" s="1">
         <v>46075</v>
       </c>
@@ -4649,7 +4643,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="508" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A508" s="1">
         <v>46075</v>
       </c>
@@ -4657,7 +4651,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="509" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A509" s="1">
         <v>46075</v>
       </c>
@@ -4665,7 +4659,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="510" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A510" s="1">
         <v>46075</v>
       </c>
@@ -4673,7 +4667,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="511" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A511" s="1">
         <v>46082</v>
       </c>
@@ -4681,7 +4675,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="512" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A512" s="1">
         <v>46082</v>
       </c>
@@ -4689,7 +4683,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="513" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A513" s="1">
         <v>46082</v>
       </c>
@@ -4697,7 +4691,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="514" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A514" s="1">
         <v>46082</v>
       </c>
@@ -4705,7 +4699,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="515" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A515" s="1">
         <v>46089</v>
       </c>
@@ -4713,7 +4707,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="516" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A516" s="1">
         <v>46089</v>
       </c>
@@ -4721,7 +4715,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="517" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A517" s="1">
         <v>46089</v>
       </c>
@@ -4729,7 +4723,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="518" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A518" s="1">
         <v>46089</v>
       </c>
@@ -4737,7 +4731,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="519" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A519" s="1">
         <v>46096</v>
       </c>
@@ -4745,7 +4739,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="520" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A520" s="1">
         <v>46096</v>
       </c>
@@ -4753,7 +4747,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="521" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A521" s="1">
         <v>46096</v>
       </c>
@@ -4761,15 +4755,15 @@
         <v>63</v>
       </c>
     </row>
-    <row r="522" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A522" s="1">
         <v>46096</v>
       </c>
       <c r="B522" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="523" spans="1:2" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A523" s="1">
         <v>46103</v>
       </c>
@@ -4777,7 +4771,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="524" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A524" s="1">
         <v>46103</v>
       </c>
@@ -4785,7 +4779,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="525" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A525" s="1">
         <v>46103</v>
       </c>
@@ -4793,7 +4787,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="526" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A526" s="1">
         <v>46103</v>
       </c>
@@ -4801,7 +4795,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="527" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A527" s="1">
         <v>46110</v>
       </c>
@@ -4809,7 +4803,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="528" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A528" s="1">
         <v>46110</v>
       </c>
@@ -4817,7 +4811,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="529" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A529" s="1">
         <v>46110</v>
       </c>
@@ -4825,7 +4819,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="530" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A530" s="1">
         <v>46110</v>
       </c>
@@ -4833,7 +4827,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="531" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A531" s="1">
         <v>46117</v>
       </c>
@@ -4841,7 +4835,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="532" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A532" s="1">
         <v>46117</v>
       </c>
@@ -4849,7 +4843,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="533" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A533" s="1">
         <v>46117</v>
       </c>
@@ -4857,7 +4851,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="534" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A534" s="1">
         <v>46117</v>
       </c>
@@ -4865,7 +4859,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="535" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A535" s="1">
         <v>46117</v>
       </c>
@@ -4873,7 +4867,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="536" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A536" s="1">
         <v>46124</v>
       </c>
@@ -4881,7 +4875,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="537" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A537" s="1">
         <v>46124</v>
       </c>
@@ -4889,7 +4883,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="538" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A538" s="1">
         <v>46124</v>
       </c>
@@ -4897,7 +4891,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="539" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A539" s="1">
         <v>46124</v>
       </c>
@@ -4905,15 +4899,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="540" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A540" s="1">
         <v>46131</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="541" spans="1:2" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A541" s="1">
         <v>46131</v>
       </c>
@@ -4921,7 +4915,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="542" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A542" s="1">
         <v>46131</v>
       </c>
@@ -4929,7 +4923,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="543" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A543" s="1">
         <v>46131</v>
       </c>
@@ -4937,7 +4931,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="544" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A544" s="1">
         <v>46138</v>
       </c>
@@ -4945,7 +4939,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="545" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A545" s="1">
         <v>46138</v>
       </c>
@@ -4953,7 +4947,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="546" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A546" s="1">
         <v>46138</v>
       </c>
@@ -4961,7 +4955,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="547" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A547" s="1">
         <v>46138</v>
       </c>
@@ -4969,7 +4963,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="548" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A548" s="1">
         <v>46145</v>
       </c>
@@ -4977,7 +4971,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="549" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A549" s="1">
         <v>46145</v>
       </c>
@@ -4985,7 +4979,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="550" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A550" s="1">
         <v>46145</v>
       </c>
@@ -4993,7 +4987,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="551" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A551" s="1">
         <v>46145</v>
       </c>
@@ -5001,7 +4995,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="552" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A552" s="1">
         <v>46152</v>
       </c>
@@ -5009,7 +5003,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="553" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A553" s="1">
         <v>46152</v>
       </c>
@@ -5017,7 +5011,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="554" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A554" s="1">
         <v>46152</v>
       </c>
@@ -5025,7 +5019,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="555" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A555" s="1">
         <v>46152</v>
       </c>
@@ -5033,7 +5027,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="556" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A556" s="1">
         <v>46159</v>
       </c>
@@ -5041,7 +5035,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="557" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A557" s="1">
         <v>46159</v>
       </c>
@@ -5049,7 +5043,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="558" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A558" s="1">
         <v>46159</v>
       </c>
@@ -5057,7 +5051,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="559" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A559" s="1">
         <v>46159</v>
       </c>
@@ -5065,7 +5059,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="560" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A560" s="1">
         <v>46166</v>
       </c>
@@ -5073,7 +5067,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="561" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A561" s="1">
         <v>46166</v>
       </c>
@@ -5081,7 +5075,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="562" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A562" s="1">
         <v>46166</v>
       </c>
@@ -5089,7 +5083,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="563" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A563" s="1">
         <v>46166</v>
       </c>
@@ -5097,7 +5091,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="564" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A564" s="1">
         <v>46173</v>
       </c>
@@ -5105,7 +5099,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="565" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A565" s="1">
         <v>46173</v>
       </c>
@@ -5113,7 +5107,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="566" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A566" s="1">
         <v>46173</v>
       </c>
@@ -5121,7 +5115,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="567" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A567" s="1">
         <v>46173</v>
       </c>
@@ -5129,7 +5123,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="568" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A568" s="1">
         <v>46180</v>
       </c>
@@ -5137,7 +5131,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="569" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A569" s="1">
         <v>46180</v>
       </c>
@@ -5145,7 +5139,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="570" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A570" s="1">
         <v>46180</v>
       </c>
@@ -5153,7 +5147,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="571" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A571" s="1">
         <v>46180</v>
       </c>
@@ -5161,7 +5155,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="572" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A572" s="1">
         <v>46187</v>
       </c>
@@ -5169,7 +5163,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="573" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A573" s="1">
         <v>46187</v>
       </c>
@@ -5177,7 +5171,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="574" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A574" s="1">
         <v>46187</v>
       </c>
@@ -5185,7 +5179,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="575" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A575" s="1">
         <v>46187</v>
       </c>
@@ -5193,7 +5187,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="576" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A576" s="1">
         <v>46194</v>
       </c>
@@ -5201,15 +5195,15 @@
         <v>77</v>
       </c>
     </row>
-    <row r="577" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A577" s="1">
         <v>46194</v>
       </c>
       <c r="B577" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="578" spans="1:2" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="578" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A578" s="1">
         <v>46194</v>
       </c>
@@ -5217,7 +5211,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="579" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A579" s="1">
         <v>46194</v>
       </c>
@@ -5225,7 +5219,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="580" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A580" s="1">
         <v>46201</v>
       </c>
@@ -5233,7 +5227,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="581" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A581" s="1">
         <v>46201</v>
       </c>
@@ -5241,7 +5235,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="582" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A582" s="1">
         <v>46201</v>
       </c>
@@ -5249,7 +5243,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="583" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A583" s="1">
         <v>46201</v>
       </c>

--- a/backend/data/songs-source-06-2026.xlsx
+++ b/backend/data/songs-source-06-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\josefprochazka\repos-ubuntu\songs-names-analyzer\backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD74778-891C-46B3-9BCA-A04F0F29A00D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DC11F15-2339-4EB1-B264-AD82BA50A9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DATA" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="93">
   <si>
     <t>Ježíš Kristus, On je král</t>
   </si>
@@ -348,7 +348,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -358,6 +358,7 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
@@ -580,10 +581,10 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F583"/>
-  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F599"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1">
         <v>45186</v>
       </c>
@@ -591,7 +592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>45186</v>
       </c>
@@ -599,7 +600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>45186</v>
       </c>
@@ -607,7 +608,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>45186</v>
       </c>
@@ -615,7 +616,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>45186</v>
       </c>
@@ -623,7 +624,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>45193</v>
       </c>
@@ -631,7 +632,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>45193</v>
       </c>
@@ -639,7 +640,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>45193</v>
       </c>
@@ -647,7 +648,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>45193</v>
       </c>
@@ -659,7 +660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>45193</v>
       </c>
@@ -667,7 +668,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>45200</v>
       </c>
@@ -675,7 +676,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>45200</v>
       </c>
@@ -683,7 +684,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>45200</v>
       </c>
@@ -691,7 +692,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>45200</v>
       </c>
@@ -699,7 +700,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>45200</v>
       </c>
@@ -707,7 +708,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>45207</v>
       </c>
@@ -715,7 +716,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>45207</v>
       </c>
@@ -723,7 +724,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>45207</v>
       </c>
@@ -731,7 +732,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>45214</v>
       </c>
@@ -739,7 +740,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>45214</v>
       </c>
@@ -747,7 +748,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>45214</v>
       </c>
@@ -755,7 +756,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>45221</v>
       </c>
@@ -763,7 +764,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>45221</v>
       </c>
@@ -771,7 +772,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>45221</v>
       </c>
@@ -779,7 +780,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>45228</v>
       </c>
@@ -787,7 +788,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>45228</v>
       </c>
@@ -795,7 +796,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>45228</v>
       </c>
@@ -803,7 +804,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>45235</v>
       </c>
@@ -811,7 +812,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>45235</v>
       </c>
@@ -819,7 +820,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>45235</v>
       </c>
@@ -827,7 +828,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>45242</v>
       </c>
@@ -835,7 +836,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>45242</v>
       </c>
@@ -843,7 +844,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>45242</v>
       </c>
@@ -851,7 +852,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>45249</v>
       </c>
@@ -859,7 +860,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>45249</v>
       </c>
@@ -867,7 +868,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>45249</v>
       </c>
@@ -875,7 +876,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
         <v>45256</v>
       </c>
@@ -883,7 +884,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
         <v>45256</v>
       </c>
@@ -891,7 +892,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
         <v>45256</v>
       </c>
@@ -899,7 +900,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
         <v>45256</v>
       </c>
@@ -907,7 +908,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>45263</v>
       </c>
@@ -915,7 +916,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>45263</v>
       </c>
@@ -923,7 +924,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>45263</v>
       </c>
@@ -931,7 +932,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>45263</v>
       </c>
@@ -939,7 +940,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
         <v>45270</v>
       </c>
@@ -947,7 +948,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
         <v>45270</v>
       </c>
@@ -955,7 +956,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="4">
         <v>45270</v>
       </c>
@@ -963,7 +964,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="4">
         <v>45270</v>
       </c>
@@ -971,7 +972,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="4">
         <v>45277</v>
       </c>
@@ -979,7 +980,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="4">
         <v>45277</v>
       </c>
@@ -987,7 +988,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
         <v>45277</v>
       </c>
@@ -995,7 +996,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
         <v>45277</v>
       </c>
@@ -1003,7 +1004,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
         <v>45284</v>
       </c>
@@ -1011,7 +1012,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="4">
         <v>45284</v>
       </c>
@@ -1019,7 +1020,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
         <v>45284</v>
       </c>
@@ -1027,7 +1028,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
         <v>45284</v>
       </c>
@@ -1035,7 +1036,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
         <v>45291</v>
       </c>
@@ -1043,7 +1044,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="4">
         <v>45291</v>
       </c>
@@ -1051,7 +1052,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="4">
         <v>45291</v>
       </c>
@@ -1059,7 +1060,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="4">
         <v>45291</v>
       </c>
@@ -1067,7 +1068,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>45298</v>
       </c>
@@ -1075,7 +1076,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>45298</v>
       </c>
@@ -1083,7 +1084,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>45298</v>
       </c>
@@ -1091,7 +1092,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>45298</v>
       </c>
@@ -1099,7 +1100,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>45305</v>
       </c>
@@ -1107,7 +1108,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>45305</v>
       </c>
@@ -1115,7 +1116,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>45305</v>
       </c>
@@ -1123,7 +1124,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>45305</v>
       </c>
@@ -1131,7 +1132,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>45312</v>
       </c>
@@ -1139,7 +1140,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>45312</v>
       </c>
@@ -1147,7 +1148,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>45312</v>
       </c>
@@ -1155,7 +1156,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>45312</v>
       </c>
@@ -1163,7 +1164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>45319</v>
       </c>
@@ -1171,7 +1172,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>45319</v>
       </c>
@@ -1179,7 +1180,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>45319</v>
       </c>
@@ -1187,7 +1188,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="76" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <v>45319</v>
       </c>
@@ -1195,7 +1196,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <v>45326</v>
       </c>
@@ -1203,7 +1204,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>45326</v>
       </c>
@@ -1211,7 +1212,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>45326</v>
       </c>
@@ -1219,7 +1220,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="80" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>45326</v>
       </c>
@@ -1227,7 +1228,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>45333</v>
       </c>
@@ -1235,7 +1236,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="82" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>45333</v>
       </c>
@@ -1243,7 +1244,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="83" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>45333</v>
       </c>
@@ -1251,7 +1252,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="84" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>45333</v>
       </c>
@@ -1259,7 +1260,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="85" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>45340</v>
       </c>
@@ -1267,7 +1268,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>45340</v>
       </c>
@@ -1275,7 +1276,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="87" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>45340</v>
       </c>
@@ -1283,7 +1284,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="88" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>45340</v>
       </c>
@@ -1291,7 +1292,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="89" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>45347</v>
       </c>
@@ -1299,7 +1300,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="90" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <v>45347</v>
       </c>
@@ -1307,7 +1308,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="91" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <v>45347</v>
       </c>
@@ -1315,7 +1316,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="92" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <v>45347</v>
       </c>
@@ -1323,7 +1324,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="93" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <v>45354</v>
       </c>
@@ -1331,7 +1332,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="94" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <v>45354</v>
       </c>
@@ -1339,7 +1340,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="95" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <v>45354</v>
       </c>
@@ -1347,7 +1348,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="96" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <v>45354</v>
       </c>
@@ -1355,7 +1356,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="97" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <v>45361</v>
       </c>
@@ -1363,7 +1364,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="98" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>45361</v>
       </c>
@@ -1371,7 +1372,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="99" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <v>45361</v>
       </c>
@@ -1379,7 +1380,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="100" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>45361</v>
       </c>
@@ -1387,7 +1388,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>45368</v>
       </c>
@@ -1395,7 +1396,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="102" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>45368</v>
       </c>
@@ -1403,7 +1404,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="103" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>45368</v>
       </c>
@@ -1411,7 +1412,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>45368</v>
       </c>
@@ -1419,7 +1420,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="105" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <v>45375</v>
       </c>
@@ -1427,7 +1428,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="106" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
         <v>45375</v>
       </c>
@@ -1435,7 +1436,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="107" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
         <v>45375</v>
       </c>
@@ -1443,7 +1444,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="108" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <v>45375</v>
       </c>
@@ -1451,7 +1452,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <v>45382</v>
       </c>
@@ -1459,7 +1460,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="110" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <v>45382</v>
       </c>
@@ -1467,7 +1468,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="111" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <v>45382</v>
       </c>
@@ -1475,7 +1476,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="112" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <v>45382</v>
       </c>
@@ -1483,7 +1484,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="113" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <v>45389</v>
       </c>
@@ -1491,7 +1492,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="114" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <v>45389</v>
       </c>
@@ -1499,7 +1500,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="115" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <v>45389</v>
       </c>
@@ -1507,7 +1508,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="116" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <v>45389</v>
       </c>
@@ -1515,7 +1516,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="117" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <v>45396</v>
       </c>
@@ -1523,7 +1524,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="118" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <v>45396</v>
       </c>
@@ -1531,7 +1532,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="119" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <v>45396</v>
       </c>
@@ -1539,7 +1540,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="120" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <v>45396</v>
       </c>
@@ -1547,7 +1548,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="121" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <v>45403</v>
       </c>
@@ -1555,7 +1556,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="122" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <v>45403</v>
       </c>
@@ -1563,7 +1564,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="123" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <v>45403</v>
       </c>
@@ -1571,7 +1572,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="124" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <v>45403</v>
       </c>
@@ -1579,7 +1580,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <v>45410</v>
       </c>
@@ -1587,7 +1588,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="126" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <v>45410</v>
       </c>
@@ -1595,7 +1596,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="127" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
         <v>45410</v>
       </c>
@@ -1603,7 +1604,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="128" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
         <v>45410</v>
       </c>
@@ -1611,7 +1612,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="129" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <v>45417</v>
       </c>
@@ -1619,7 +1620,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="130" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <v>45417</v>
       </c>
@@ -1627,7 +1628,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="131" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <v>45417</v>
       </c>
@@ -1635,7 +1636,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="132" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <v>45417</v>
       </c>
@@ -1643,7 +1644,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="133" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <v>45424</v>
       </c>
@@ -1651,7 +1652,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="134" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <v>45424</v>
       </c>
@@ -1659,7 +1660,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="135" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <v>45424</v>
       </c>
@@ -1667,7 +1668,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="136" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <v>45424</v>
       </c>
@@ -1675,7 +1676,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="137" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <v>45431</v>
       </c>
@@ -1683,7 +1684,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="138" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <v>45431</v>
       </c>
@@ -1691,7 +1692,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="139" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <v>45431</v>
       </c>
@@ -1699,7 +1700,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="140" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <v>45431</v>
       </c>
@@ -1707,7 +1708,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="141" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <v>45438</v>
       </c>
@@ -1715,7 +1716,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="142" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <v>45438</v>
       </c>
@@ -1723,7 +1724,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="143" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <v>45438</v>
       </c>
@@ -1731,7 +1732,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="144" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <v>45438</v>
       </c>
@@ -1739,7 +1740,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="145" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
         <v>45445</v>
       </c>
@@ -1747,7 +1748,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="146" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
         <v>45445</v>
       </c>
@@ -1755,7 +1756,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="147" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
         <v>45445</v>
       </c>
@@ -1763,7 +1764,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="148" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
         <v>45445</v>
       </c>
@@ -1771,7 +1772,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="149" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
         <v>45452</v>
       </c>
@@ -1779,7 +1780,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="150" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
         <v>45452</v>
       </c>
@@ -1787,7 +1788,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="151" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
         <v>45452</v>
       </c>
@@ -1795,7 +1796,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="152" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A152" s="1">
         <v>45452</v>
       </c>
@@ -1803,7 +1804,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="153" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
         <v>45459</v>
       </c>
@@ -1811,7 +1812,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="154" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
         <v>45459</v>
       </c>
@@ -1819,7 +1820,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="155" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A155" s="1">
         <v>45459</v>
       </c>
@@ -1827,7 +1828,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="156" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A156" s="1">
         <v>45459</v>
       </c>
@@ -1835,7 +1836,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="157" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A157" s="1">
         <v>45466</v>
       </c>
@@ -1843,7 +1844,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="158" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
         <v>45466</v>
       </c>
@@ -1851,7 +1852,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="159" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A159" s="1">
         <v>45466</v>
       </c>
@@ -1859,7 +1860,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
         <v>45466</v>
       </c>
@@ -1867,7 +1868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
         <v>45473</v>
       </c>
@@ -1875,7 +1876,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="162" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
         <v>45473</v>
       </c>
@@ -1883,7 +1884,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="163" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A163" s="1">
         <v>45473</v>
       </c>
@@ -1891,7 +1892,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="164" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
         <v>45473</v>
       </c>
@@ -1899,7 +1900,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="165" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A165" s="1">
         <v>45480</v>
       </c>
@@ -1907,7 +1908,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="166" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A166" s="1">
         <v>45480</v>
       </c>
@@ -1915,7 +1916,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="167" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A167" s="1">
         <v>45480</v>
       </c>
@@ -1923,7 +1924,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="168" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A168" s="1">
         <v>45480</v>
       </c>
@@ -1931,7 +1932,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="169" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A169" s="1">
         <v>45487</v>
       </c>
@@ -1939,7 +1940,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="170" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A170" s="1">
         <v>45487</v>
       </c>
@@ -1947,7 +1948,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="171" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A171" s="1">
         <v>45487</v>
       </c>
@@ -1955,7 +1956,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="172" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A172" s="1">
         <v>45487</v>
       </c>
@@ -1963,7 +1964,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="173" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A173" s="1">
         <v>45494</v>
       </c>
@@ -1971,7 +1972,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="174" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
         <v>45494</v>
       </c>
@@ -1979,7 +1980,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="175" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A175" s="1">
         <v>45494</v>
       </c>
@@ -1987,7 +1988,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="176" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A176" s="1">
         <v>45494</v>
       </c>
@@ -1995,7 +1996,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="177" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
         <v>45494</v>
       </c>
@@ -2003,7 +2004,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="178" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A178" s="1">
         <v>45501</v>
       </c>
@@ -2011,7 +2012,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="179" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A179" s="1">
         <v>45501</v>
       </c>
@@ -2019,7 +2020,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="180" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A180" s="1">
         <v>45501</v>
       </c>
@@ -2027,7 +2028,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="181" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A181" s="1">
         <v>45501</v>
       </c>
@@ -2035,7 +2036,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="182" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A182" s="1">
         <v>45508</v>
       </c>
@@ -2043,7 +2044,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="183" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A183" s="1">
         <v>45508</v>
       </c>
@@ -2051,7 +2052,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="184" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A184" s="1">
         <v>45508</v>
       </c>
@@ -2059,7 +2060,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="185" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A185" s="1">
         <v>45508</v>
       </c>
@@ -2067,7 +2068,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="186" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
         <v>45515</v>
       </c>
@@ -2075,7 +2076,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="187" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
         <v>45515</v>
       </c>
@@ -2083,7 +2084,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="188" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A188" s="1">
         <v>45515</v>
       </c>
@@ -2091,7 +2092,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="189" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A189" s="1">
         <v>45515</v>
       </c>
@@ -2099,7 +2100,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="190" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
         <v>45522</v>
       </c>
@@ -2107,7 +2108,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="191" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A191" s="1">
         <v>45522</v>
       </c>
@@ -2115,7 +2116,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="192" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A192" s="1">
         <v>45522</v>
       </c>
@@ -2123,7 +2124,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="193" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A193" s="1">
         <v>45522</v>
       </c>
@@ -2131,7 +2132,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="194" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A194" s="1">
         <v>45529</v>
       </c>
@@ -2139,7 +2140,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="195" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A195" s="1">
         <v>45529</v>
       </c>
@@ -2147,7 +2148,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="196" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A196" s="1">
         <v>45529</v>
       </c>
@@ -2155,7 +2156,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="197" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A197" s="1">
         <v>45529</v>
       </c>
@@ -2163,7 +2164,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="198" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A198" s="1">
         <v>45543</v>
       </c>
@@ -2171,7 +2172,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="199" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A199" s="1">
         <v>45543</v>
       </c>
@@ -2179,7 +2180,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="200" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A200" s="1">
         <v>45543</v>
       </c>
@@ -2187,7 +2188,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="201" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A201" s="1">
         <v>45543</v>
       </c>
@@ -2195,7 +2196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A202" s="1">
         <v>45550</v>
       </c>
@@ -2203,7 +2204,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="203" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A203" s="1">
         <v>45550</v>
       </c>
@@ -2211,7 +2212,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="204" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A204" s="1">
         <v>45550</v>
       </c>
@@ -2219,7 +2220,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="205" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A205" s="1">
         <v>45550</v>
       </c>
@@ -2227,7 +2228,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="206" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
         <v>45557</v>
       </c>
@@ -2235,7 +2236,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="207" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A207" s="1">
         <v>45557</v>
       </c>
@@ -2243,7 +2244,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="208" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A208" s="1">
         <v>45557</v>
       </c>
@@ -2251,7 +2252,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="209" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A209" s="1">
         <v>45557</v>
       </c>
@@ -2259,7 +2260,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="210" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A210" s="1">
         <v>45564</v>
       </c>
@@ -2267,7 +2268,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="211" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A211" s="1">
         <v>45564</v>
       </c>
@@ -2275,7 +2276,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="212" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A212" s="1">
         <v>45564</v>
       </c>
@@ -2283,7 +2284,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="213" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A213" s="1">
         <v>45564</v>
       </c>
@@ -2291,7 +2292,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="214" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A214" s="1">
         <v>45571</v>
       </c>
@@ -2299,7 +2300,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="215" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A215" s="1">
         <v>45571</v>
       </c>
@@ -2307,7 +2308,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="216" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A216" s="1">
         <v>45571</v>
       </c>
@@ -2315,7 +2316,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="217" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A217" s="1">
         <v>45571</v>
       </c>
@@ -2323,7 +2324,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="218" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A218" s="4">
         <v>45578</v>
       </c>
@@ -2331,7 +2332,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="219" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A219" s="4">
         <v>45578</v>
       </c>
@@ -2339,7 +2340,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="220" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A220" s="4">
         <v>45578</v>
       </c>
@@ -2347,7 +2348,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="221" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A221" s="4">
         <v>45578</v>
       </c>
@@ -2355,7 +2356,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="222" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
         <v>45585</v>
       </c>
@@ -2363,7 +2364,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="223" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A223" s="4">
         <v>45585</v>
       </c>
@@ -2371,7 +2372,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="224" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A224" s="4">
         <v>45585</v>
       </c>
@@ -2379,7 +2380,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="225" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A225" s="4">
         <v>45585</v>
       </c>
@@ -2387,7 +2388,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="226" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A226" s="4">
         <v>45592</v>
       </c>
@@ -2395,7 +2396,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="227" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A227" s="4">
         <v>45592</v>
       </c>
@@ -2403,7 +2404,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="228" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A228" s="4">
         <v>45592</v>
       </c>
@@ -2411,7 +2412,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="229" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A229" s="4">
         <v>45592</v>
       </c>
@@ -2419,7 +2420,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="230" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A230" s="1">
         <v>45599</v>
       </c>
@@ -2427,7 +2428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A231" s="1">
         <v>45599</v>
       </c>
@@ -2435,7 +2436,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="232" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A232" s="1">
         <v>45599</v>
       </c>
@@ -2443,7 +2444,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="233" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A233" s="1">
         <v>45599</v>
       </c>
@@ -2451,7 +2452,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="234" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A234" s="4">
         <v>45606</v>
       </c>
@@ -2459,7 +2460,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="235" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A235" s="4">
         <v>45606</v>
       </c>
@@ -2467,7 +2468,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="236" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A236" s="4">
         <v>45606</v>
       </c>
@@ -2475,7 +2476,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="237" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A237" s="4">
         <v>45606</v>
       </c>
@@ -2483,7 +2484,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="238" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A238" s="4">
         <v>45606</v>
       </c>
@@ -2491,7 +2492,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="239" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A239" s="4">
         <v>45613</v>
       </c>
@@ -2499,7 +2500,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="240" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A240" s="4">
         <v>45613</v>
       </c>
@@ -2507,7 +2508,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="241" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A241" s="4">
         <v>45613</v>
       </c>
@@ -2515,7 +2516,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="242" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A242" s="4">
         <v>45613</v>
       </c>
@@ -2523,7 +2524,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="243" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A243" s="4">
         <v>45620</v>
       </c>
@@ -2531,7 +2532,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="244" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
         <v>45620</v>
       </c>
@@ -2539,7 +2540,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="245" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A245" s="4">
         <v>45620</v>
       </c>
@@ -2547,7 +2548,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="246" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A246" s="4">
         <v>45620</v>
       </c>
@@ -2555,7 +2556,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="247" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A247" s="4">
         <v>45620</v>
       </c>
@@ -2563,7 +2564,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="248" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A248" s="1">
         <v>45627</v>
       </c>
@@ -2571,7 +2572,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="249" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A249" s="1">
         <v>45627</v>
       </c>
@@ -2579,7 +2580,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="250" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A250" s="1">
         <v>45627</v>
       </c>
@@ -2587,7 +2588,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="251" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A251" s="1">
         <v>45627</v>
       </c>
@@ -2595,7 +2596,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="252" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A252" s="1">
         <v>45634</v>
       </c>
@@ -2603,7 +2604,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="253" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A253" s="1">
         <v>45634</v>
       </c>
@@ -2611,7 +2612,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="254" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A254" s="1">
         <v>45634</v>
       </c>
@@ -2619,7 +2620,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="255" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A255" s="1">
         <v>45634</v>
       </c>
@@ -2627,7 +2628,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="256" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A256" s="4">
         <v>45641</v>
       </c>
@@ -2635,7 +2636,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="257" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A257" s="4">
         <v>45641</v>
       </c>
@@ -2643,7 +2644,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="258" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A258" s="4">
         <v>45641</v>
       </c>
@@ -2651,7 +2652,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="259" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A259" s="4">
         <v>45641</v>
       </c>
@@ -2659,7 +2660,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="260" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A260" s="4">
         <v>45648</v>
       </c>
@@ -2667,7 +2668,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="261" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A261" s="4">
         <v>45648</v>
       </c>
@@ -2675,7 +2676,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="262" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A262" s="4">
         <v>45648</v>
       </c>
@@ -2683,7 +2684,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="263" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A263" s="4">
         <v>45648</v>
       </c>
@@ -2691,7 +2692,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="264" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A264" s="4">
         <v>45648</v>
       </c>
@@ -2699,7 +2700,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="265" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A265" s="4">
         <v>45655</v>
       </c>
@@ -2707,7 +2708,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="266" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
         <v>45655</v>
       </c>
@@ -2715,7 +2716,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="267" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A267" s="4">
         <v>45655</v>
       </c>
@@ -2723,7 +2724,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="268" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A268" s="4">
         <v>45655</v>
       </c>
@@ -2731,7 +2732,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="269" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A269" s="1">
         <v>45662</v>
       </c>
@@ -2739,7 +2740,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="270" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A270" s="1">
         <v>45662</v>
       </c>
@@ -2747,7 +2748,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="271" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A271" s="1">
         <v>45662</v>
       </c>
@@ -2755,7 +2756,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="272" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A272" s="1">
         <v>45662</v>
       </c>
@@ -2763,7 +2764,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="273" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A273" s="1">
         <v>45669</v>
       </c>
@@ -2771,7 +2772,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="274" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A274" s="1">
         <v>45669</v>
       </c>
@@ -2779,7 +2780,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="275" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A275" s="1">
         <v>45669</v>
       </c>
@@ -2787,7 +2788,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="276" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A276" s="1">
         <v>45669</v>
       </c>
@@ -2795,7 +2796,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="277" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A277" s="1">
         <v>45676</v>
       </c>
@@ -2803,7 +2804,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="278" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A278" s="1">
         <v>45676</v>
       </c>
@@ -2811,7 +2812,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="279" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A279" s="1">
         <v>45676</v>
       </c>
@@ -2819,7 +2820,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="280" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A280" s="1">
         <v>45676</v>
       </c>
@@ -2827,7 +2828,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="281" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A281" s="1">
         <v>45683</v>
       </c>
@@ -2835,7 +2836,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="282" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A282" s="1">
         <v>45683</v>
       </c>
@@ -2843,7 +2844,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="283" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A283" s="1">
         <v>45683</v>
       </c>
@@ -2851,7 +2852,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="284" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A284" s="1">
         <v>45683</v>
       </c>
@@ -2859,7 +2860,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="285" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A285" s="1">
         <v>45690</v>
       </c>
@@ -2867,7 +2868,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="286" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A286" s="1">
         <v>45690</v>
       </c>
@@ -2875,7 +2876,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="287" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A287" s="1">
         <v>45690</v>
       </c>
@@ -2883,7 +2884,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="288" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A288" s="1">
         <v>45690</v>
       </c>
@@ -2891,7 +2892,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="289" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A289" s="1">
         <v>45697</v>
       </c>
@@ -2899,7 +2900,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="290" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A290" s="1">
         <v>45697</v>
       </c>
@@ -2907,7 +2908,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="291" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A291" s="1">
         <v>45697</v>
       </c>
@@ -2915,7 +2916,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="292" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A292" s="1">
         <v>45697</v>
       </c>
@@ -2923,7 +2924,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="293" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A293" s="1">
         <v>45704</v>
       </c>
@@ -2931,7 +2932,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="294" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A294" s="1">
         <v>45704</v>
       </c>
@@ -2939,7 +2940,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="295" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A295" s="1">
         <v>45704</v>
       </c>
@@ -2947,7 +2948,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="296" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A296" s="1">
         <v>45704</v>
       </c>
@@ -2955,7 +2956,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="297" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A297" s="1">
         <v>45711</v>
       </c>
@@ -2963,7 +2964,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="298" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A298" s="1">
         <v>45711</v>
       </c>
@@ -2971,7 +2972,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="299" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A299" s="1">
         <v>45711</v>
       </c>
@@ -2979,7 +2980,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="300" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A300" s="1">
         <v>45711</v>
       </c>
@@ -2987,7 +2988,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="301" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A301" s="1">
         <v>45718</v>
       </c>
@@ -2995,7 +2996,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="302" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A302" s="1">
         <v>45718</v>
       </c>
@@ -3003,7 +3004,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="303" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A303" s="1">
         <v>45718</v>
       </c>
@@ -3011,7 +3012,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="304" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A304" s="1">
         <v>45718</v>
       </c>
@@ -3019,7 +3020,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="305" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A305" s="1">
         <v>45725</v>
       </c>
@@ -3027,7 +3028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="306" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A306" s="1">
         <v>45725</v>
       </c>
@@ -3035,7 +3036,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="307" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A307" s="1">
         <v>45725</v>
       </c>
@@ -3043,7 +3044,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="308" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A308" s="1">
         <v>45725</v>
       </c>
@@ -3051,7 +3052,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="309" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A309" s="1">
         <v>45732</v>
       </c>
@@ -3059,7 +3060,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="310" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A310" s="1">
         <v>45732</v>
       </c>
@@ -3067,7 +3068,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="311" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A311" s="1">
         <v>45732</v>
       </c>
@@ -3075,7 +3076,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="312" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A312" s="1">
         <v>45732</v>
       </c>
@@ -3083,7 +3084,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="313" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A313" s="1">
         <v>45739</v>
       </c>
@@ -3091,7 +3092,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="314" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A314" s="1">
         <v>45739</v>
       </c>
@@ -3099,7 +3100,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="315" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A315" s="1">
         <v>45739</v>
       </c>
@@ -3107,7 +3108,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="316" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A316" s="1">
         <v>45739</v>
       </c>
@@ -3115,7 +3116,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="317" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A317" s="1">
         <v>45746</v>
       </c>
@@ -3123,7 +3124,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="318" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A318" s="1">
         <v>45746</v>
       </c>
@@ -3131,7 +3132,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="319" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A319" s="1">
         <v>45746</v>
       </c>
@@ -3139,7 +3140,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="320" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A320" s="1">
         <v>45746</v>
       </c>
@@ -3147,7 +3148,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="321" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A321" s="1">
         <v>45753</v>
       </c>
@@ -3155,7 +3156,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="322" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A322" s="1">
         <v>45753</v>
       </c>
@@ -3163,7 +3164,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="323" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A323" s="1">
         <v>45753</v>
       </c>
@@ -3171,7 +3172,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="324" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A324" s="1">
         <v>45753</v>
       </c>
@@ -3179,7 +3180,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="325" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A325" s="1">
         <v>45760</v>
       </c>
@@ -3187,7 +3188,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="326" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A326" s="1">
         <v>45760</v>
       </c>
@@ -3195,7 +3196,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="327" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A327" s="1">
         <v>45760</v>
       </c>
@@ -3203,7 +3204,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="328" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A328" s="1">
         <v>45760</v>
       </c>
@@ -3211,7 +3212,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="329" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A329" s="1">
         <v>45767</v>
       </c>
@@ -3219,7 +3220,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="330" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A330" s="1">
         <v>45767</v>
       </c>
@@ -3227,7 +3228,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="331" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A331" s="1">
         <v>45767</v>
       </c>
@@ -3235,7 +3236,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="332" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A332" s="1">
         <v>45767</v>
       </c>
@@ -3243,7 +3244,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="333" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A333" s="1">
         <v>45767</v>
       </c>
@@ -3251,7 +3252,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="334" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A334" s="1">
         <v>45774</v>
       </c>
@@ -3259,7 +3260,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="335" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A335" s="1">
         <v>45774</v>
       </c>
@@ -3267,7 +3268,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="336" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A336" s="1">
         <v>45774</v>
       </c>
@@ -3275,7 +3276,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="337" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A337" s="1">
         <v>45774</v>
       </c>
@@ -3283,7 +3284,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="338" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A338" s="1">
         <v>45781</v>
       </c>
@@ -3291,7 +3292,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="339" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A339" s="1">
         <v>45781</v>
       </c>
@@ -3299,7 +3300,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="340" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A340" s="1">
         <v>45781</v>
       </c>
@@ -3307,7 +3308,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="341" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A341" s="1">
         <v>45781</v>
       </c>
@@ -3315,7 +3316,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="342" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A342" s="1">
         <v>45788</v>
       </c>
@@ -3323,7 +3324,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="343" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A343" s="1">
         <v>45788</v>
       </c>
@@ -3331,7 +3332,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="344" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A344" s="1">
         <v>45788</v>
       </c>
@@ -3339,7 +3340,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="345" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A345" s="1">
         <v>45788</v>
       </c>
@@ -3347,7 +3348,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="346" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A346" s="1">
         <v>45795</v>
       </c>
@@ -3355,7 +3356,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="347" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A347" s="1">
         <v>45795</v>
       </c>
@@ -3363,7 +3364,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="348" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A348" s="1">
         <v>45795</v>
       </c>
@@ -3371,7 +3372,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="349" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A349" s="1">
         <v>45795</v>
       </c>
@@ -3379,7 +3380,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="350" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A350" s="1">
         <v>45802</v>
       </c>
@@ -3387,7 +3388,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="351" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A351" s="1">
         <v>45802</v>
       </c>
@@ -3395,7 +3396,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="352" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A352" s="1">
         <v>45802</v>
       </c>
@@ -3403,7 +3404,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="353" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A353" s="1">
         <v>45802</v>
       </c>
@@ -3411,7 +3412,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="354" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A354" s="1">
         <v>45809</v>
       </c>
@@ -3419,7 +3420,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="355" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A355" s="1">
         <v>45809</v>
       </c>
@@ -3427,7 +3428,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="356" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A356" s="1">
         <v>45809</v>
       </c>
@@ -3435,7 +3436,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="357" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A357" s="1">
         <v>45809</v>
       </c>
@@ -3443,7 +3444,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="358" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A358" s="1">
         <v>45816</v>
       </c>
@@ -3451,7 +3452,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="359" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A359" s="1">
         <v>45816</v>
       </c>
@@ -3459,7 +3460,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="360" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A360" s="1">
         <v>45816</v>
       </c>
@@ -3467,7 +3468,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="361" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A361" s="1">
         <v>45816</v>
       </c>
@@ -3475,7 +3476,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="362" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A362" s="1">
         <v>45823</v>
       </c>
@@ -3483,7 +3484,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="363" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A363" s="1">
         <v>45823</v>
       </c>
@@ -3491,7 +3492,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="364" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A364" s="1">
         <v>45823</v>
       </c>
@@ -3499,7 +3500,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="365" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A365" s="1">
         <v>45823</v>
       </c>
@@ -3507,7 +3508,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="366" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A366" s="1">
         <v>45830</v>
       </c>
@@ -3515,7 +3516,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="367" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A367" s="1">
         <v>45830</v>
       </c>
@@ -3523,7 +3524,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="368" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A368" s="1">
         <v>45830</v>
       </c>
@@ -3531,7 +3532,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="369" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A369" s="1">
         <v>45830</v>
       </c>
@@ -3539,7 +3540,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="370" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A370" s="1">
         <v>45837</v>
       </c>
@@ -3547,7 +3548,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="371" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A371" s="1">
         <v>45837</v>
       </c>
@@ -3555,7 +3556,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="372" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A372" s="1">
         <v>45837</v>
       </c>
@@ -3563,7 +3564,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="373" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A373" s="1">
         <v>45837</v>
       </c>
@@ -3571,7 +3572,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="374" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A374" s="1">
         <v>45844</v>
       </c>
@@ -3579,7 +3580,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="375" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A375" s="1">
         <v>45844</v>
       </c>
@@ -3587,7 +3588,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="376" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A376" s="1">
         <v>45844</v>
       </c>
@@ -3595,7 +3596,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="377" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A377" s="1">
         <v>45844</v>
       </c>
@@ -3603,7 +3604,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="378" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A378" s="1">
         <v>45851</v>
       </c>
@@ -3611,7 +3612,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="379" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A379" s="1">
         <v>45851</v>
       </c>
@@ -3619,7 +3620,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="380" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A380" s="1">
         <v>45851</v>
       </c>
@@ -3627,7 +3628,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="381" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A381" s="1">
         <v>45851</v>
       </c>
@@ -3635,7 +3636,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="382" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A382" s="1">
         <v>45851</v>
       </c>
@@ -3643,7 +3644,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="383" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A383" s="1">
         <v>45858</v>
       </c>
@@ -3651,7 +3652,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="384" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A384" s="1">
         <v>45858</v>
       </c>
@@ -3659,7 +3660,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="385" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A385" s="1">
         <v>45858</v>
       </c>
@@ -3667,7 +3668,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="386" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A386" s="1">
         <v>45858</v>
       </c>
@@ -3675,7 +3676,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="387" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A387" s="1">
         <v>45865</v>
       </c>
@@ -3683,7 +3684,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="388" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A388" s="1">
         <v>45865</v>
       </c>
@@ -3691,7 +3692,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="389" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A389" s="1">
         <v>45865</v>
       </c>
@@ -3699,7 +3700,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="390" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A390" s="1">
         <v>45865</v>
       </c>
@@ -3707,7 +3708,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="391" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A391" s="1">
         <v>45872</v>
       </c>
@@ -3715,7 +3716,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="392" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A392" s="1">
         <v>45872</v>
       </c>
@@ -3723,7 +3724,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="393" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A393" s="1">
         <v>45872</v>
       </c>
@@ -3731,7 +3732,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="394" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A394" s="1">
         <v>45872</v>
       </c>
@@ -3739,7 +3740,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="395" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A395" s="1">
         <v>45879</v>
       </c>
@@ -3747,7 +3748,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="396" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A396" s="1">
         <v>45879</v>
       </c>
@@ -3755,7 +3756,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="397" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A397" s="1">
         <v>45879</v>
       </c>
@@ -3763,7 +3764,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="398" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A398" s="1">
         <v>45879</v>
       </c>
@@ -3771,7 +3772,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="399" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A399" s="1">
         <v>45886</v>
       </c>
@@ -3779,7 +3780,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="400" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A400" s="1">
         <v>45886</v>
       </c>
@@ -3787,7 +3788,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="401" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A401" s="1">
         <v>45886</v>
       </c>
@@ -3795,7 +3796,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="402" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A402" s="1">
         <v>45886</v>
       </c>
@@ -3803,7 +3804,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="403" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A403" s="1">
         <v>45893</v>
       </c>
@@ -3811,7 +3812,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="404" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A404" s="1">
         <v>45893</v>
       </c>
@@ -3819,7 +3820,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="405" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A405" s="1">
         <v>45893</v>
       </c>
@@ -3827,7 +3828,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="406" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A406" s="1">
         <v>45893</v>
       </c>
@@ -3835,7 +3836,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="407" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A407" s="1">
         <v>45907</v>
       </c>
@@ -3843,7 +3844,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="408" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A408" s="1">
         <v>45907</v>
       </c>
@@ -3851,7 +3852,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="409" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A409" s="1">
         <v>45907</v>
       </c>
@@ -3859,7 +3860,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="410" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A410" s="1">
         <v>45907</v>
       </c>
@@ -3867,7 +3868,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="411" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A411" s="1">
         <v>45907</v>
       </c>
@@ -3875,7 +3876,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="412" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A412" s="1">
         <v>45914</v>
       </c>
@@ -3883,7 +3884,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="413" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A413" s="1">
         <v>45914</v>
       </c>
@@ -3891,7 +3892,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="414" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A414" s="1">
         <v>45914</v>
       </c>
@@ -3899,7 +3900,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="415" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A415" s="1">
         <v>45914</v>
       </c>
@@ -3907,7 +3908,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="416" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A416" s="1">
         <v>45921</v>
       </c>
@@ -3915,7 +3916,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="417" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A417" s="1">
         <v>45921</v>
       </c>
@@ -3923,7 +3924,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="418" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A418" s="1">
         <v>45921</v>
       </c>
@@ -3931,7 +3932,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="419" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A419" s="1">
         <v>45921</v>
       </c>
@@ -3939,7 +3940,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="420" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A420" s="1">
         <v>45928</v>
       </c>
@@ -3947,7 +3948,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="421" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A421" s="1">
         <v>45928</v>
       </c>
@@ -3955,7 +3956,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="422" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A422" s="1">
         <v>45928</v>
       </c>
@@ -3963,7 +3964,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="423" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A423" s="1">
         <v>45928</v>
       </c>
@@ -3971,7 +3972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A424" s="1">
         <v>45935</v>
       </c>
@@ -3979,7 +3980,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="425" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A425" s="1">
         <v>45935</v>
       </c>
@@ -3987,7 +3988,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="426" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A426" s="1">
         <v>45935</v>
       </c>
@@ -3995,7 +3996,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="427" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A427" s="1">
         <v>45935</v>
       </c>
@@ -4003,7 +4004,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="428" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A428" s="4">
         <v>45942</v>
       </c>
@@ -4011,7 +4012,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="429" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A429" s="4">
         <v>45942</v>
       </c>
@@ -4019,7 +4020,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="430" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A430" s="4">
         <v>45942</v>
       </c>
@@ -4027,7 +4028,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="431" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
         <v>45942</v>
       </c>
@@ -4035,7 +4036,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="432" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A432" s="4">
         <v>45949</v>
       </c>
@@ -4043,7 +4044,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="433" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A433" s="4">
         <v>45949</v>
       </c>
@@ -4051,7 +4052,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="434" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A434" s="4">
         <v>45949</v>
       </c>
@@ -4059,7 +4060,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="435" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A435" s="4">
         <v>45949</v>
       </c>
@@ -4067,7 +4068,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="436" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A436" s="4">
         <v>45956</v>
       </c>
@@ -4075,7 +4076,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="437" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A437" s="4">
         <v>45956</v>
       </c>
@@ -4083,7 +4084,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="438" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A438" s="4">
         <v>45956</v>
       </c>
@@ -4091,7 +4092,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="439" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A439" s="4">
         <v>45956</v>
       </c>
@@ -4099,7 +4100,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="440" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A440" s="1">
         <v>45963</v>
       </c>
@@ -4107,7 +4108,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="441" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A441" s="1">
         <v>45963</v>
       </c>
@@ -4115,7 +4116,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="442" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A442" s="1">
         <v>45963</v>
       </c>
@@ -4123,7 +4124,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="443" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A443" s="1">
         <v>45963</v>
       </c>
@@ -4131,7 +4132,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="444" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A444" s="1">
         <v>45970</v>
       </c>
@@ -4139,7 +4140,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="445" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A445" s="1">
         <v>45970</v>
       </c>
@@ -4147,7 +4148,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="446" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A446" s="1">
         <v>45970</v>
       </c>
@@ -4155,7 +4156,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="447" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A447" s="1">
         <v>45970</v>
       </c>
@@ -4163,7 +4164,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="448" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A448" s="4">
         <v>45977</v>
       </c>
@@ -4171,7 +4172,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="449" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A449" s="4">
         <v>45977</v>
       </c>
@@ -4179,7 +4180,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="450" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A450" s="4">
         <v>45977</v>
       </c>
@@ -4187,7 +4188,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="451" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A451" s="4">
         <v>45977</v>
       </c>
@@ -4195,7 +4196,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="452" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A452" s="4">
         <v>45984</v>
       </c>
@@ -4203,7 +4204,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="453" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
         <v>45984</v>
       </c>
@@ -4211,7 +4212,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="454" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A454" s="4">
         <v>45984</v>
       </c>
@@ -4219,7 +4220,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="455" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A455" s="4">
         <v>45984</v>
       </c>
@@ -4227,7 +4228,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="456" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A456" s="4">
         <v>45991</v>
       </c>
@@ -4235,7 +4236,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="457" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A457" s="4">
         <v>45991</v>
       </c>
@@ -4243,7 +4244,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="458" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A458" s="4">
         <v>45991</v>
       </c>
@@ -4251,7 +4252,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="459" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A459" s="4">
         <v>45991</v>
       </c>
@@ -4259,7 +4260,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="460" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A460" s="1">
         <v>45998</v>
       </c>
@@ -4267,7 +4268,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="461" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A461" s="1">
         <v>45998</v>
       </c>
@@ -4275,7 +4276,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="462" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A462" s="1">
         <v>45998</v>
       </c>
@@ -4283,7 +4284,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="463" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A463" s="1">
         <v>45998</v>
       </c>
@@ -4291,7 +4292,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="464" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
         <v>46005</v>
       </c>
@@ -4299,7 +4300,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="465" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A465" s="4">
         <v>46005</v>
       </c>
@@ -4307,7 +4308,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="466" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A466" s="4">
         <v>46005</v>
       </c>
@@ -4315,7 +4316,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="467" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A467" s="4">
         <v>46005</v>
       </c>
@@ -4323,7 +4324,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="468" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A468" s="4">
         <v>46012</v>
       </c>
@@ -4331,7 +4332,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="469" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A469" s="4">
         <v>46012</v>
       </c>
@@ -4339,7 +4340,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="470" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A470" s="4">
         <v>46012</v>
       </c>
@@ -4347,7 +4348,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="471" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A471" s="4">
         <v>46012</v>
       </c>
@@ -4355,7 +4356,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="472" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A472" s="4">
         <v>46012</v>
       </c>
@@ -4363,7 +4364,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="473" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A473" s="4">
         <v>46012</v>
       </c>
@@ -4371,7 +4372,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="474" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A474" s="4">
         <v>46012</v>
       </c>
@@ -4379,7 +4380,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="475" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
         <v>46019</v>
       </c>
@@ -4387,7 +4388,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="476" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A476" s="4">
         <v>46019</v>
       </c>
@@ -4395,7 +4396,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="477" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A477" s="4">
         <v>46019</v>
       </c>
@@ -4403,7 +4404,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="478" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A478" s="4">
         <v>46019</v>
       </c>
@@ -4411,7 +4412,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="479" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A479" s="1">
         <v>46026</v>
       </c>
@@ -4419,7 +4420,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="480" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A480" s="1">
         <v>46026</v>
       </c>
@@ -4427,7 +4428,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="481" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A481" s="1">
         <v>46026</v>
       </c>
@@ -4435,7 +4436,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="482" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A482" s="1">
         <v>46026</v>
       </c>
@@ -4443,7 +4444,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="483" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A483" s="1">
         <v>46033</v>
       </c>
@@ -4451,7 +4452,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="484" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A484" s="1">
         <v>46033</v>
       </c>
@@ -4459,7 +4460,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="485" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A485" s="1">
         <v>46033</v>
       </c>
@@ -4467,7 +4468,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="486" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A486" s="1">
         <v>46033</v>
       </c>
@@ -4475,7 +4476,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="487" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A487" s="1">
         <v>46040</v>
       </c>
@@ -4483,7 +4484,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="488" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A488" s="1">
         <v>46040</v>
       </c>
@@ -4491,7 +4492,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="489" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A489" s="1">
         <v>46040</v>
       </c>
@@ -4499,7 +4500,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="490" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A490" s="1">
         <v>46040</v>
       </c>
@@ -4507,7 +4508,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="491" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A491" s="1">
         <v>46047</v>
       </c>
@@ -4515,7 +4516,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="492" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A492" s="1">
         <v>46047</v>
       </c>
@@ -4523,7 +4524,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="493" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A493" s="1">
         <v>46047</v>
       </c>
@@ -4531,7 +4532,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="494" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A494" s="1">
         <v>46047</v>
       </c>
@@ -4539,7 +4540,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="495" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A495" s="1">
         <v>46054</v>
       </c>
@@ -4547,7 +4548,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="496" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A496" s="1">
         <v>46054</v>
       </c>
@@ -4555,7 +4556,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="497" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A497" s="1">
         <v>46054</v>
       </c>
@@ -4563,7 +4564,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="498" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A498" s="1">
         <v>46054</v>
       </c>
@@ -4571,7 +4572,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="499" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A499" s="1">
         <v>46061</v>
       </c>
@@ -4579,7 +4580,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="500" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A500" s="1">
         <v>46061</v>
       </c>
@@ -4587,7 +4588,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="501" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A501" s="1">
         <v>46061</v>
       </c>
@@ -4595,7 +4596,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="502" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A502" s="1">
         <v>46061</v>
       </c>
@@ -4603,7 +4604,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="503" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A503" s="1">
         <v>46068</v>
       </c>
@@ -4611,7 +4612,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="504" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A504" s="1">
         <v>46068</v>
       </c>
@@ -4619,7 +4620,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="505" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A505" s="1">
         <v>46068</v>
       </c>
@@ -4627,7 +4628,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="506" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A506" s="1">
         <v>46068</v>
       </c>
@@ -4635,7 +4636,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="507" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A507" s="1">
         <v>46075</v>
       </c>
@@ -4643,7 +4644,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="508" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A508" s="1">
         <v>46075</v>
       </c>
@@ -4651,7 +4652,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="509" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A509" s="1">
         <v>46075</v>
       </c>
@@ -4659,7 +4660,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="510" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A510" s="1">
         <v>46075</v>
       </c>
@@ -4667,7 +4668,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="511" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A511" s="1">
         <v>46082</v>
       </c>
@@ -4675,7 +4676,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="512" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A512" s="1">
         <v>46082</v>
       </c>
@@ -4683,7 +4684,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="513" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A513" s="1">
         <v>46082</v>
       </c>
@@ -4691,7 +4692,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="514" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A514" s="1">
         <v>46082</v>
       </c>
@@ -4699,7 +4700,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="515" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A515" s="1">
         <v>46089</v>
       </c>
@@ -4707,7 +4708,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="516" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A516" s="1">
         <v>46089</v>
       </c>
@@ -4715,7 +4716,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="517" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A517" s="1">
         <v>46089</v>
       </c>
@@ -4723,7 +4724,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="518" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A518" s="1">
         <v>46089</v>
       </c>
@@ -4731,7 +4732,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="519" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A519" s="1">
         <v>46096</v>
       </c>
@@ -4739,7 +4740,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="520" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A520" s="1">
         <v>46096</v>
       </c>
@@ -4747,7 +4748,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="521" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A521" s="1">
         <v>46096</v>
       </c>
@@ -4755,7 +4756,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="522" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A522" s="1">
         <v>46096</v>
       </c>
@@ -4763,7 +4764,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="523" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A523" s="1">
         <v>46103</v>
       </c>
@@ -4771,7 +4772,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="524" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A524" s="1">
         <v>46103</v>
       </c>
@@ -4779,7 +4780,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="525" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A525" s="1">
         <v>46103</v>
       </c>
@@ -4787,7 +4788,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="526" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A526" s="1">
         <v>46103</v>
       </c>
@@ -4795,7 +4796,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="527" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A527" s="1">
         <v>46110</v>
       </c>
@@ -4803,7 +4804,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="528" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A528" s="1">
         <v>46110</v>
       </c>
@@ -4811,7 +4812,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="529" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A529" s="1">
         <v>46110</v>
       </c>
@@ -4819,7 +4820,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="530" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A530" s="1">
         <v>46110</v>
       </c>
@@ -4827,7 +4828,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="531" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A531" s="1">
         <v>46117</v>
       </c>
@@ -4835,7 +4836,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="532" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A532" s="1">
         <v>46117</v>
       </c>
@@ -4843,7 +4844,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="533" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A533" s="1">
         <v>46117</v>
       </c>
@@ -4851,7 +4852,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="534" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A534" s="1">
         <v>46117</v>
       </c>
@@ -4859,7 +4860,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="535" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A535" s="1">
         <v>46117</v>
       </c>
@@ -4867,7 +4868,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="536" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A536" s="1">
         <v>46124</v>
       </c>
@@ -4875,7 +4876,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="537" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A537" s="1">
         <v>46124</v>
       </c>
@@ -4883,7 +4884,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="538" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A538" s="1">
         <v>46124</v>
       </c>
@@ -4891,7 +4892,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="539" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A539" s="1">
         <v>46124</v>
       </c>
@@ -4899,7 +4900,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="540" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A540" s="1">
         <v>46131</v>
       </c>
@@ -4907,7 +4908,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="541" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A541" s="1">
         <v>46131</v>
       </c>
@@ -4915,7 +4916,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="542" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A542" s="1">
         <v>46131</v>
       </c>
@@ -4923,7 +4924,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="543" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A543" s="1">
         <v>46131</v>
       </c>
@@ -4931,7 +4932,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="544" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A544" s="1">
         <v>46138</v>
       </c>
@@ -4939,7 +4940,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="545" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A545" s="1">
         <v>46138</v>
       </c>
@@ -4947,7 +4948,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="546" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A546" s="1">
         <v>46138</v>
       </c>
@@ -4955,7 +4956,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="547" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A547" s="1">
         <v>46138</v>
       </c>
@@ -4963,7 +4964,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="548" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A548" s="1">
         <v>46145</v>
       </c>
@@ -4971,7 +4972,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="549" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A549" s="1">
         <v>46145</v>
       </c>
@@ -4979,7 +4980,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="550" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A550" s="1">
         <v>46145</v>
       </c>
@@ -4987,7 +4988,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="551" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A551" s="1">
         <v>46145</v>
       </c>
@@ -4995,7 +4996,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="552" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A552" s="1">
         <v>46152</v>
       </c>
@@ -5003,7 +5004,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="553" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A553" s="1">
         <v>46152</v>
       </c>
@@ -5011,7 +5012,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="554" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A554" s="1">
         <v>46152</v>
       </c>
@@ -5019,7 +5020,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="555" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A555" s="1">
         <v>46152</v>
       </c>
@@ -5027,7 +5028,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="556" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A556" s="1">
         <v>46159</v>
       </c>
@@ -5035,7 +5036,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="557" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A557" s="1">
         <v>46159</v>
       </c>
@@ -5043,7 +5044,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="558" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A558" s="1">
         <v>46159</v>
       </c>
@@ -5051,7 +5052,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="559" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A559" s="1">
         <v>46159</v>
       </c>
@@ -5059,7 +5060,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="560" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A560" s="1">
         <v>46166</v>
       </c>
@@ -5067,7 +5068,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="561" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A561" s="1">
         <v>46166</v>
       </c>
@@ -5075,7 +5076,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="562" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A562" s="1">
         <v>46166</v>
       </c>
@@ -5083,7 +5084,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="563" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A563" s="1">
         <v>46166</v>
       </c>
@@ -5091,7 +5092,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="564" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A564" s="1">
         <v>46173</v>
       </c>
@@ -5099,7 +5100,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="565" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A565" s="1">
         <v>46173</v>
       </c>
@@ -5107,7 +5108,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="566" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A566" s="1">
         <v>46173</v>
       </c>
@@ -5115,7 +5116,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="567" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A567" s="1">
         <v>46173</v>
       </c>
@@ -5123,7 +5124,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="568" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A568" s="1">
         <v>46180</v>
       </c>
@@ -5131,7 +5132,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="569" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A569" s="1">
         <v>46180</v>
       </c>
@@ -5139,7 +5140,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="570" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A570" s="1">
         <v>46180</v>
       </c>
@@ -5147,7 +5148,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="571" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A571" s="1">
         <v>46180</v>
       </c>
@@ -5155,7 +5156,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="572" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A572" s="1">
         <v>46187</v>
       </c>
@@ -5163,7 +5164,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="573" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A573" s="1">
         <v>46187</v>
       </c>
@@ -5171,7 +5172,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="574" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A574" s="1">
         <v>46187</v>
       </c>
@@ -5179,7 +5180,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="575" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A575" s="1">
         <v>46187</v>
       </c>
@@ -5187,7 +5188,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="576" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A576" s="1">
         <v>46194</v>
       </c>
@@ -5195,7 +5196,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="577" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A577" s="1">
         <v>46194</v>
       </c>
@@ -5203,7 +5204,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="578" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A578" s="1">
         <v>46194</v>
       </c>
@@ -5211,7 +5212,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="579" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A579" s="1">
         <v>46194</v>
       </c>
@@ -5219,7 +5220,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="580" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A580" s="1">
         <v>46201</v>
       </c>
@@ -5227,7 +5228,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="581" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A581" s="1">
         <v>46201</v>
       </c>
@@ -5235,7 +5236,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="582" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A582" s="1">
         <v>46201</v>
       </c>
@@ -5243,12 +5244,140 @@
         <v>65</v>
       </c>
     </row>
-    <row r="583" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A583" s="1">
         <v>46201</v>
       </c>
       <c r="B583" s="2" t="s">
         <v>81</v>
+      </c>
+    </row>
+    <row r="584" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A584" s="5">
+        <v>46208</v>
+      </c>
+      <c r="B584" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="585" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A585" s="5">
+        <v>46208</v>
+      </c>
+      <c r="B585" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="586" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A586" s="5">
+        <v>46208</v>
+      </c>
+      <c r="B586" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="587" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A587" s="5">
+        <v>46208</v>
+      </c>
+      <c r="B587" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="588" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A588" s="5">
+        <v>46215</v>
+      </c>
+      <c r="B588" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="589" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A589" s="5">
+        <v>46215</v>
+      </c>
+      <c r="B589" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="590" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A590" s="5">
+        <v>46215</v>
+      </c>
+      <c r="B590" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="591" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A591" s="5">
+        <v>46215</v>
+      </c>
+      <c r="B591" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="592" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A592" s="5">
+        <v>46222</v>
+      </c>
+      <c r="B592" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="593" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A593" s="5">
+        <v>46222</v>
+      </c>
+      <c r="B593" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="594" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A594" s="5">
+        <v>46222</v>
+      </c>
+      <c r="B594" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="595" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A595" s="5">
+        <v>46222</v>
+      </c>
+      <c r="B595" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="596" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A596" s="5">
+        <v>46229</v>
+      </c>
+      <c r="B596" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="597" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A597" s="5">
+        <v>46229</v>
+      </c>
+      <c r="B597" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="598" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A598" s="5">
+        <v>46229</v>
+      </c>
+      <c r="B598" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="599" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A599" s="5">
+        <v>46229</v>
+      </c>
+      <c r="B599" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
